--- a/09_Risk_Management/_template_RISK.xlsx
+++ b/09_Risk_Management/_template_RISK.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t xml:space="preserve">[PORTFOLIO] — Risk Management Model</t>
   </si>
@@ -89,16 +89,28 @@
     <t xml:space="preserve">VaR as % of portfolio</t>
   </si>
   <si>
+    <t xml:space="preserve">Expected Shortfall / CVaR (1-day, $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytic ES under normality: sigma x phi(Z) / (1-confidence). Always &gt;= VaR — it's the average loss GIVEN that VaR is breached, not just the threshold.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Historical VaR (alternative method)</t>
   </si>
   <si>
-    <t xml:space="preserve">Enter trailing daily P&amp;L observations below (min 100 recommended); </t>
+    <t xml:space="preserve">Enter trailing daily P&amp;L observations below (min 100 recommended)</t>
   </si>
   <si>
     <t xml:space="preserve">Historical VaR = PERCENTILE of P&amp;L distribution at (1-confidence)</t>
   </si>
   <si>
     <t xml:space="preserve">Historical VaR ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical CVaR / ES ($, avg of losses beyond the VaR percentile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily P&amp;L ($)</t>
   </si>
   <si>
     <t xml:space="preserve">Stress Scenarios</t>
@@ -313,88 +325,96 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -651,48 +671,48 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -712,124 +732,448 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:E122"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <f aca="false">NORMSINV(C7)</f>
         <v>1.64485362695147</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <f aca="false">C5*C6*C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="13" t="n">
         <f aca="false">C12*SQRT(C8)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="14" t="str">
+      <c r="C14" s="15" t="str">
         <f aca="false">IFERROR(C13/C5,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="C15" s="13" t="n">
+        <f aca="false">IFERROR(C5*C6*NORMDIST(C11,0,1,FALSE())/(1-C7),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="s">
-        <v>22</v>
+      <c r="B18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>23</v>
+      <c r="B19" s="14" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="11" t="str">
-        <f aca="false">IFERROR(-PERCENTILE(E20:E119,1-C7),"[fill in P&amp;L history in col E]")</f>
-        <v>[fill in P&amp;L history in col E]</v>
-      </c>
+      <c r="B20" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="13" t="str">
+        <f aca="false">IFERROR(-PERCENTILE(E23:E122,1-C7),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <f aca="false">IFERROR(-AVERAGEIF(E23:E122,"&lt;="&amp;PERCENTILE(E23:E122,1-C7)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="16"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="16"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="16"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="16"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="16"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E37" s="16"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="16"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="16"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="16"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="16"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="16"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="16"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="16"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E48" s="16"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E49" s="16"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E50" s="16"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E51" s="16"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E52" s="16"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E53" s="16"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E54" s="16"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E55" s="16"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E56" s="16"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E57" s="16"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E58" s="16"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="16"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="16"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E61" s="16"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="16"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="16"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E64" s="16"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E65" s="16"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E66" s="16"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E67" s="16"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E68" s="16"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E69" s="16"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E70" s="16"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E71" s="16"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E72" s="16"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E73" s="16"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E74" s="16"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E75" s="16"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E76" s="16"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E77" s="16"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E78" s="16"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E79" s="16"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E80" s="16"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E81" s="16"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E82" s="16"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E83" s="16"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E84" s="16"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E85" s="16"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E86" s="16"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E87" s="16"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E88" s="16"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E89" s="16"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E90" s="16"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E91" s="16"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E92" s="16"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E93" s="16"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E94" s="16"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E95" s="16"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E96" s="16"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E97" s="16"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E98" s="16"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E99" s="16"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E100" s="16"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E101" s="16"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E102" s="16"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E103" s="16"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E104" s="16"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E105" s="16"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E106" s="16"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E107" s="16"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E108" s="16"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E109" s="16"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E110" s="16"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E111" s="16"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E112" s="16"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E113" s="16"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E114" s="16"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E115" s="16"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E116" s="16"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E117" s="16"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E118" s="16"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E119" s="16"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E120" s="16"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E121" s="16"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E122" s="16"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -848,107 +1192,107 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:E9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>25</v>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>29</v>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="17" t="n">
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <v>-0.4</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <f aca="false">VaR!$C$5*C5</f>
         <v>-0</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>31</v>
+      <c r="E5" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="17" t="n">
+      <c r="B6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="19" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <f aca="false">VaR!$C$5*C6</f>
         <v>-0</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>31</v>
+      <c r="E6" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="17" t="n">
+      <c r="B7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="19" t="n">
         <v>-0.08</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <f aca="false">VaR!$C$5*C7</f>
         <v>-0</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>31</v>
+      <c r="E7" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="17" t="n">
+      <c r="B8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="19" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">VaR!$C$5*C8</f>
         <v>-0</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>31</v>
+      <c r="E8" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="17" t="n">
+      <c r="B9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="19" t="n">
         <v>-0.25</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">VaR!$C$5*C9</f>
         <v>-0</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>31</v>
+      <c r="E9" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -968,159 +1312,159 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>36</v>
+      <c r="B2" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="18" t="n">
+      <c r="B4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="20" t="n">
         <v>0.9</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="20" t="n">
         <v>0.95</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="20" t="n">
         <v>0.975</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="20" t="n">
         <v>0.99</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="20" t="n">
         <v>0.995</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <f aca="false">VaR!$C$5*B5*NORMSINV(C4)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <f aca="false">VaR!$C$5*B5*NORMSINV(D4)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <f aca="false">VaR!$C$5*B5*NORMSINV(E4)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <f aca="false">VaR!$C$5*B5*NORMSINV(F4)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="12" t="n">
         <f aca="false">VaR!$C$5*B5*NORMSINV(G4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="21" t="n">
         <v>0.015</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <f aca="false">VaR!$C$5*B6*NORMSINV(C4)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <f aca="false">VaR!$C$5*B6*NORMSINV(D4)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <f aca="false">VaR!$C$5*B6*NORMSINV(E4)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <f aca="false">VaR!$C$5*B6*NORMSINV(F4)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <f aca="false">VaR!$C$5*B6*NORMSINV(G4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="21" t="n">
         <v>0.02</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <f aca="false">VaR!$C$5*B7*NORMSINV(C4)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <f aca="false">VaR!$C$5*B7*NORMSINV(D4)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <f aca="false">VaR!$C$5*B7*NORMSINV(E4)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <f aca="false">VaR!$C$5*B7*NORMSINV(F4)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <f aca="false">VaR!$C$5*B7*NORMSINV(G4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <f aca="false">VaR!$C$5*B8*NORMSINV(C4)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">VaR!$C$5*B8*NORMSINV(D4)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <f aca="false">VaR!$C$5*B8*NORMSINV(E4)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <f aca="false">VaR!$C$5*B8*NORMSINV(F4)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <f aca="false">VaR!$C$5*B8*NORMSINV(G4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <f aca="false">VaR!$C$5*B9*NORMSINV(C4)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">VaR!$C$5*B9*NORMSINV(D4)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <f aca="false">VaR!$C$5*B9*NORMSINV(E4)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <f aca="false">VaR!$C$5*B9*NORMSINV(F4)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <f aca="false">VaR!$C$5*B9*NORMSINV(G4)</f>
         <v>0</v>
       </c>
@@ -1142,106 +1486,106 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>38</v>
+      <c r="B2" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="15" t="s">
+      <c r="B4" s="17" t="s">
         <v>43</v>
       </c>
+      <c r="C4" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/09_Risk_Management/_template_RISK.xlsx
+++ b/09_Risk_Management/_template_RISK.xlsx
@@ -1,122 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Positions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Factors" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="VaR &amp; ES" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Risk Contributions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Stress" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Liquidity" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="P&amp;L Explain" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Limits" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Checks" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sources" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="RefreshLog" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factors" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VaR &amp; ES" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Contributions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liquidity" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L Explain" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limits" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
     <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
     <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%;[RED]\(0.0%\);\-"/>
-    <numFmt numFmtId="165" formatCode="0.00%;[RED]\(0.00%\);\-"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0.0;[RED]&quot;($&quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0\x;[RED]\(0.0&quot;x)&quot;;\-"/>
+    <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
+    <numFmt numFmtId="165" formatCode="0.00%;[Red](0.00%);-"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
+    <numFmt numFmtId="167" formatCode="0.0x;[Red](0.0x);-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF111827"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF008000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -141,14 +112,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -171,22 +140,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="FF111827"/>
+        <color rgb="00111827"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thin">
@@ -194,323 +155,184 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF111827"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -518,294 +340,404 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="36" customWidth="1" style="28" min="2" max="2"/>
-    <col width="46" customWidth="1" style="28" min="3" max="3"/>
-    <col width="12" customWidth="1" style="28" min="4" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>[PORTFOLIO] — Multi-Asset Risk Model</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="31" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Portfolio / desk:</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>[Name]</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Risk horizon:</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>1-day and stressed liquidation</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Next limit review:</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Refresh cadence:</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Intraday / daily</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Active scenario:</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Units:</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>$ in millions unless noted</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="33" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Modeling conventions</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="B14" s="34" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Blue text / yellow fill</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Hardcoded input or selected scenario</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="29">
-      <c r="B15" s="31" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Formula / same-sheet calculation</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="29">
-      <c r="B16" s="36" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Cross-sheet formula / link</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="29">
-      <c r="B17" s="31" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>PASS / REVIEW / FAIL must remain visible</t>
         </is>
@@ -817,251 +749,253 @@
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Downside"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="30" customWidth="1" style="28" min="2" max="2"/>
-    <col width="13" customWidth="1" style="28" min="3" max="8"/>
-    <col width="16" customWidth="1" style="28" min="9" max="9"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Portfolio Stress Matrix</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Vol</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Liquidity</t>
         </is>
       </c>
-      <c r="I4" s="42" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Global risk-off</t>
         </is>
       </c>
-      <c r="C5" s="47" t="n">
+      <c r="C5" s="13" t="n">
         <v>-0.18</v>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="D5" s="13" t="n">
         <v>-0.015</v>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="13" t="n">
         <v>-0.025</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="F5" s="13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="G5" s="47" t="n">
+      <c r="G5" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="H5" s="51" t="n">
+      <c r="H5" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="16">
         <f>(Factors!$C$5*C5+Factors!$C$6*D5+Factors!$C$7*E5+Factors!$C$8*F5+Factors!$C$9*G5)-(ABS(Positions!$D$5)*MAX(0,Positions!$M$5-1)+ABS(Positions!$D$6)*MAX(0,Positions!$M$6-1)+ABS(Positions!$D$7)*MAX(0,Positions!$M$7-1)+ABS(Positions!$D$8)*MAX(0,Positions!$M$8-1)+ABS(Positions!$D$9)*MAX(0,Positions!$M$9-1)+ABS(Positions!$D$10)*MAX(0,Positions!$M$10-1)+ABS(Positions!$D$11)*MAX(0,Positions!$M$11-1)+ABS(Positions!$D$12)*MAX(0,Positions!$M$12-1)+ABS(Positions!$D$13)*MAX(0,Positions!$M$13-1)+ABS(Positions!$D$14)*MAX(0,Positions!$M$14-1)+ABS(Positions!$D$15)*MAX(0,Positions!$M$15-1)+ABS(Positions!$D$16)*MAX(0,Positions!$M$16-1))*Assumptions!$E$17*(1-H5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Inflation / rates shock</t>
         </is>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="13" t="n">
         <v>0.012</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="H6" s="51" t="n">
+      <c r="H6" s="17" t="n">
         <v>0.7</v>
       </c>
-      <c r="I6" s="50">
+      <c r="I6" s="16">
         <f>(Factors!$C$5*C6+Factors!$C$6*D6+Factors!$C$7*E6+Factors!$C$8*F6+Factors!$C$9*G6)-(ABS(Positions!$D$5)*MAX(0,Positions!$M$5-1)+ABS(Positions!$D$6)*MAX(0,Positions!$M$6-1)+ABS(Positions!$D$7)*MAX(0,Positions!$M$7-1)+ABS(Positions!$D$8)*MAX(0,Positions!$M$8-1)+ABS(Positions!$D$9)*MAX(0,Positions!$M$9-1)+ABS(Positions!$D$10)*MAX(0,Positions!$M$10-1)+ABS(Positions!$D$11)*MAX(0,Positions!$M$11-1)+ABS(Positions!$D$12)*MAX(0,Positions!$M$12-1)+ABS(Positions!$D$13)*MAX(0,Positions!$M$13-1)+ABS(Positions!$D$14)*MAX(0,Positions!$M$14-1)+ABS(Positions!$D$15)*MAX(0,Positions!$M$15-1)+ABS(Positions!$D$16)*MAX(0,Positions!$M$16-1))*Assumptions!$E$17*(1-H6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Credit crisis</t>
         </is>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="13" t="n">
         <v>-0.12</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="13" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="13" t="n">
         <v>-0.04</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.35</v>
       </c>
-      <c r="H7" s="51" t="n">
+      <c r="H7" s="17" t="n">
         <v>0.35</v>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="16">
         <f>(Factors!$C$5*C7+Factors!$C$6*D7+Factors!$C$7*E7+Factors!$C$8*F7+Factors!$C$9*G7)-(ABS(Positions!$D$5)*MAX(0,Positions!$M$5-1)+ABS(Positions!$D$6)*MAX(0,Positions!$M$6-1)+ABS(Positions!$D$7)*MAX(0,Positions!$M$7-1)+ABS(Positions!$D$8)*MAX(0,Positions!$M$8-1)+ABS(Positions!$D$9)*MAX(0,Positions!$M$9-1)+ABS(Positions!$D$10)*MAX(0,Positions!$M$10-1)+ABS(Positions!$D$11)*MAX(0,Positions!$M$11-1)+ABS(Positions!$D$12)*MAX(0,Positions!$M$12-1)+ABS(Positions!$D$13)*MAX(0,Positions!$M$13-1)+ABS(Positions!$D$14)*MAX(0,Positions!$M$14-1)+ABS(Positions!$D$15)*MAX(0,Positions!$M$15-1)+ABS(Positions!$D$16)*MAX(0,Positions!$M$16-1))*Assumptions!$E$17*(1-H7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Dollar squeeze</t>
         </is>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="13" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="13" t="n">
         <v>0.01</v>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="13" t="n">
         <v>-0.015</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="13" t="n">
         <v>0.12</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="H8" s="51" t="n">
+      <c r="H8" s="17" t="n">
         <v>0.45</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="16">
         <f>(Factors!$C$5*C8+Factors!$C$6*D8+Factors!$C$7*E8+Factors!$C$8*F8+Factors!$C$9*G8)-(ABS(Positions!$D$5)*MAX(0,Positions!$M$5-1)+ABS(Positions!$D$6)*MAX(0,Positions!$M$6-1)+ABS(Positions!$D$7)*MAX(0,Positions!$M$7-1)+ABS(Positions!$D$8)*MAX(0,Positions!$M$8-1)+ABS(Positions!$D$9)*MAX(0,Positions!$M$9-1)+ABS(Positions!$D$10)*MAX(0,Positions!$M$10-1)+ABS(Positions!$D$11)*MAX(0,Positions!$M$11-1)+ABS(Positions!$D$12)*MAX(0,Positions!$M$12-1)+ABS(Positions!$D$13)*MAX(0,Positions!$M$13-1)+ABS(Positions!$D$14)*MAX(0,Positions!$M$14-1)+ABS(Positions!$D$15)*MAX(0,Positions!$M$15-1)+ABS(Positions!$D$16)*MAX(0,Positions!$M$16-1))*Assumptions!$E$17*(1-H8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Volatility normalization</t>
         </is>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="13" t="n">
         <v>0.005</v>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="13" t="n">
         <v>0.005</v>
       </c>
-      <c r="F9" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="47" t="n">
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H9" s="51" t="n">
+      <c r="H9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="16">
         <f>(Factors!$C$5*C9+Factors!$C$6*D9+Factors!$C$7*E9+Factors!$C$8*F9+Factors!$C$9*G9)-(ABS(Positions!$D$5)*MAX(0,Positions!$M$5-1)+ABS(Positions!$D$6)*MAX(0,Positions!$M$6-1)+ABS(Positions!$D$7)*MAX(0,Positions!$M$7-1)+ABS(Positions!$D$8)*MAX(0,Positions!$M$8-1)+ABS(Positions!$D$9)*MAX(0,Positions!$M$9-1)+ABS(Positions!$D$10)*MAX(0,Positions!$M$10-1)+ABS(Positions!$D$11)*MAX(0,Positions!$M$11-1)+ABS(Positions!$D$12)*MAX(0,Positions!$M$12-1)+ABS(Positions!$D$13)*MAX(0,Positions!$M$13-1)+ABS(Positions!$D$14)*MAX(0,Positions!$M$14-1)+ABS(Positions!$D$15)*MAX(0,Positions!$M$15-1)+ABS(Positions!$D$16)*MAX(0,Positions!$M$16-1))*Assumptions!$E$17*(1-H9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Idiosyncratic concentration</t>
         </is>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="13" t="n">
         <v>-0.25</v>
       </c>
-      <c r="D10" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="47" t="n">
+      <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F10" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="47" t="n">
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="H10" s="51" t="n">
+      <c r="H10" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="16">
         <f>(Factors!$C$5*C10+Factors!$C$6*D10+Factors!$C$7*E10+Factors!$C$8*F10+Factors!$C$9*G10)-(ABS(Positions!$D$5)*MAX(0,Positions!$M$5-1)+ABS(Positions!$D$6)*MAX(0,Positions!$M$6-1)+ABS(Positions!$D$7)*MAX(0,Positions!$M$7-1)+ABS(Positions!$D$8)*MAX(0,Positions!$M$8-1)+ABS(Positions!$D$9)*MAX(0,Positions!$M$9-1)+ABS(Positions!$D$10)*MAX(0,Positions!$M$10-1)+ABS(Positions!$D$11)*MAX(0,Positions!$M$11-1)+ABS(Positions!$D$12)*MAX(0,Positions!$M$12-1)+ABS(Positions!$D$13)*MAX(0,Positions!$M$13-1)+ABS(Positions!$D$14)*MAX(0,Positions!$M$14-1)+ABS(Positions!$D$15)*MAX(0,Positions!$M$15-1)+ABS(Positions!$D$16)*MAX(0,Positions!$M$16-1))*Assumptions!$E$17*(1-H10)</f>
         <v/>
       </c>
@@ -1070,464 +1004,462 @@
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="28" customWidth="1" style="28" min="2" max="2"/>
-    <col width="16" customWidth="1" style="28" min="3" max="3"/>
-    <col width="12" customWidth="1" style="28" min="4" max="4"/>
-    <col width="20" customWidth="1" style="28" min="5" max="5"/>
-    <col width="14" customWidth="1" style="28" min="6" max="6"/>
-    <col width="16" customWidth="1" style="28" min="7" max="7"/>
-    <col width="12" customWidth="1" style="28" min="8" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Liquidity and Liquidation Cost</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Gross notional</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>ADV participation proxy</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Impact loss</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Liquidation loss</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Illiquid?</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28">
+    <row r="5">
+      <c r="B5">
         <f>Positions!B5</f>
         <v/>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="16">
         <f>ABS(Positions!E5)</f>
         <v/>
       </c>
-      <c r="D5" s="58">
+      <c r="D5">
         <f>Positions!M5</f>
         <v/>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="14">
         <f>MIN(1,C5/MAX(1,Assumptions!$E$18)/MAX(1,D5))</f>
         <v/>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="14">
         <f>Assumptions!$E$17*E5^1.5</f>
         <v/>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="16">
         <f>C5*F5</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5">
         <f>IF(D5&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28">
+    <row r="6">
+      <c r="B6">
         <f>Positions!B6</f>
         <v/>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="16">
         <f>ABS(Positions!E6)</f>
         <v/>
       </c>
-      <c r="D6" s="58">
+      <c r="D6">
         <f>Positions!M6</f>
         <v/>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="14">
         <f>MIN(1,C6/MAX(1,Assumptions!$E$18)/MAX(1,D6))</f>
         <v/>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="14">
         <f>Assumptions!$E$17*E6^1.5</f>
         <v/>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="16">
         <f>C6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6">
         <f>IF(D6&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28">
+    <row r="7">
+      <c r="B7">
         <f>Positions!B7</f>
         <v/>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="16">
         <f>ABS(Positions!E7)</f>
         <v/>
       </c>
-      <c r="D7" s="58">
+      <c r="D7">
         <f>Positions!M7</f>
         <v/>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="14">
         <f>MIN(1,C7/MAX(1,Assumptions!$E$18)/MAX(1,D7))</f>
         <v/>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="14">
         <f>Assumptions!$E$17*E7^1.5</f>
         <v/>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="16">
         <f>C7*F7</f>
         <v/>
       </c>
-      <c r="H7" s="28">
+      <c r="H7">
         <f>IF(D7&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28">
+    <row r="8">
+      <c r="B8">
         <f>Positions!B8</f>
         <v/>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="16">
         <f>ABS(Positions!E8)</f>
         <v/>
       </c>
-      <c r="D8" s="58">
+      <c r="D8">
         <f>Positions!M8</f>
         <v/>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="14">
         <f>MIN(1,C8/MAX(1,Assumptions!$E$18)/MAX(1,D8))</f>
         <v/>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="14">
         <f>Assumptions!$E$17*E8^1.5</f>
         <v/>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="16">
         <f>C8*F8</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8">
         <f>IF(D8&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28">
+    <row r="9">
+      <c r="B9">
         <f>Positions!B9</f>
         <v/>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="16">
         <f>ABS(Positions!E9)</f>
         <v/>
       </c>
-      <c r="D9" s="58">
+      <c r="D9">
         <f>Positions!M9</f>
         <v/>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="14">
         <f>MIN(1,C9/MAX(1,Assumptions!$E$18)/MAX(1,D9))</f>
         <v/>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="14">
         <f>Assumptions!$E$17*E9^1.5</f>
         <v/>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="16">
         <f>C9*F9</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9">
         <f>IF(D9&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28">
+    <row r="10">
+      <c r="B10">
         <f>Positions!B10</f>
         <v/>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="16">
         <f>ABS(Positions!E10)</f>
         <v/>
       </c>
-      <c r="D10" s="58">
+      <c r="D10">
         <f>Positions!M10</f>
         <v/>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="14">
         <f>MIN(1,C10/MAX(1,Assumptions!$E$18)/MAX(1,D10))</f>
         <v/>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="14">
         <f>Assumptions!$E$17*E10^1.5</f>
         <v/>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="16">
         <f>C10*F10</f>
         <v/>
       </c>
-      <c r="H10" s="28">
+      <c r="H10">
         <f>IF(D10&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="B11" s="28">
+    <row r="11">
+      <c r="B11">
         <f>Positions!B11</f>
         <v/>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="16">
         <f>ABS(Positions!E11)</f>
         <v/>
       </c>
-      <c r="D11" s="58">
+      <c r="D11">
         <f>Positions!M11</f>
         <v/>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="14">
         <f>MIN(1,C11/MAX(1,Assumptions!$E$18)/MAX(1,D11))</f>
         <v/>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="14">
         <f>Assumptions!$E$17*E11^1.5</f>
         <v/>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="16">
         <f>C11*F11</f>
         <v/>
       </c>
-      <c r="H11" s="28">
+      <c r="H11">
         <f>IF(D11&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="28">
+    <row r="12">
+      <c r="B12">
         <f>Positions!B12</f>
         <v/>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="16">
         <f>ABS(Positions!E12)</f>
         <v/>
       </c>
-      <c r="D12" s="58">
+      <c r="D12">
         <f>Positions!M12</f>
         <v/>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="14">
         <f>MIN(1,C12/MAX(1,Assumptions!$E$18)/MAX(1,D12))</f>
         <v/>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="14">
         <f>Assumptions!$E$17*E12^1.5</f>
         <v/>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="16">
         <f>C12*F12</f>
         <v/>
       </c>
-      <c r="H12" s="28">
+      <c r="H12">
         <f>IF(D12&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="28">
+    <row r="13">
+      <c r="B13">
         <f>Positions!B13</f>
         <v/>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="16">
         <f>ABS(Positions!E13)</f>
         <v/>
       </c>
-      <c r="D13" s="58">
+      <c r="D13">
         <f>Positions!M13</f>
         <v/>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="14">
         <f>MIN(1,C13/MAX(1,Assumptions!$E$18)/MAX(1,D13))</f>
         <v/>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="14">
         <f>Assumptions!$E$17*E13^1.5</f>
         <v/>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="16">
         <f>C13*F13</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13">
         <f>IF(D13&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="B14" s="28">
+    <row r="14">
+      <c r="B14">
         <f>Positions!B14</f>
         <v/>
       </c>
-      <c r="C14" s="50">
+      <c r="C14" s="16">
         <f>ABS(Positions!E14)</f>
         <v/>
       </c>
-      <c r="D14" s="58">
+      <c r="D14">
         <f>Positions!M14</f>
         <v/>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="14">
         <f>MIN(1,C14/MAX(1,Assumptions!$E$18)/MAX(1,D14))</f>
         <v/>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="14">
         <f>Assumptions!$E$17*E14^1.5</f>
         <v/>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="16">
         <f>C14*F14</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14">
         <f>IF(D14&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="29">
-      <c r="B15" s="28">
+    <row r="15">
+      <c r="B15">
         <f>Positions!B15</f>
         <v/>
       </c>
-      <c r="C15" s="50">
+      <c r="C15" s="16">
         <f>ABS(Positions!E15)</f>
         <v/>
       </c>
-      <c r="D15" s="58">
+      <c r="D15">
         <f>Positions!M15</f>
         <v/>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="14">
         <f>MIN(1,C15/MAX(1,Assumptions!$E$18)/MAX(1,D15))</f>
         <v/>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="14">
         <f>Assumptions!$E$17*E15^1.5</f>
         <v/>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="16">
         <f>C15*F15</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15">
         <f>IF(D15&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="29">
-      <c r="B16" s="28">
+    <row r="16">
+      <c r="B16">
         <f>Positions!B16</f>
         <v/>
       </c>
-      <c r="C16" s="50">
+      <c r="C16" s="16">
         <f>ABS(Positions!E16)</f>
         <v/>
       </c>
-      <c r="D16" s="58">
+      <c r="D16">
         <f>Positions!M16</f>
         <v/>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="14">
         <f>MIN(1,C16/MAX(1,Assumptions!$E$18)/MAX(1,D16))</f>
         <v/>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="14">
         <f>Assumptions!$E$17*E16^1.5</f>
         <v/>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="16">
         <f>C16*F16</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16">
         <f>IF(D16&gt;5,"YES","NO")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="29">
-      <c r="B19" s="28" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Illiquid gross notional</t>
         </is>
       </c>
-      <c r="C19" s="50">
+      <c r="C19" s="16">
         <f>SUMIF(H5:H16,"YES",C5:C16)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="29">
-      <c r="B20" s="28" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Illiquid NAV ratio</t>
         </is>
       </c>
-      <c r="C20" s="48">
+      <c r="C20" s="14">
         <f>C19/Assumptions!E18</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="29">
-      <c r="B21" s="28" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Total modeled liquidation loss</t>
         </is>
       </c>
-      <c r="C21" s="50">
+      <c r="C21" s="16">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
@@ -1536,251 +1468,251 @@
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="18" customWidth="1" style="28" min="2" max="2"/>
-    <col width="16" customWidth="1" style="28" min="3" max="3"/>
-    <col width="14" customWidth="1" style="28" min="4" max="4"/>
-    <col width="18" customWidth="1" style="28" min="5" max="7"/>
-    <col width="32" customWidth="1" style="28" min="8" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Daily P&amp;L Explain</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>First-order P&amp;L</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Convexity / residual</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Explained P&amp;L</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="16">
         <f>Factors!C5</f>
         <v/>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="D5" s="13" t="n">
         <v>-0.012</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="16">
         <f>C5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="16">
         <f>E5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="28" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>delta/beta</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="16">
         <f>Factors!C6</f>
         <v/>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="13" t="n">
         <v>0.0015</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="16">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="50">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16">
         <f>E6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="16">
         <f>Factors!C7</f>
         <v/>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="13" t="n">
         <v>0.002</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="16">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="50">
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16">
         <f>E7+F7</f>
         <v/>
       </c>
-      <c r="H7" s="28" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>spread duration</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="16">
         <f>Factors!C8</f>
         <v/>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="13" t="n">
         <v>-0.006</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="16">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="50">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16">
         <f>E8+F8</f>
         <v/>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>currency delta</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="16">
         <f>Factors!C9</f>
         <v/>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="16">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="15" t="n">
         <v>0.8</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="16">
         <f>E9+F9</f>
         <v/>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>vega / convexity</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="28" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Explained P&amp;L</t>
         </is>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="16">
         <f>SUM(G5:G9)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="28" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Actual P&amp;L</t>
         </is>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="15" t="n">
         <v>-1.5</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="B14" s="28" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Unexplained P&amp;L</t>
         </is>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="16">
         <f>G13-G12</f>
         <v/>
       </c>
@@ -1789,194 +1721,194 @@
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="30" customWidth="1" style="28" min="2" max="2"/>
-    <col width="18" customWidth="1" style="28" min="3" max="5"/>
-    <col width="14" customWidth="1" style="28" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Risk Limit Dashboard</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Limit</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Headroom</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>One-day VaR</t>
         </is>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="16">
         <f>'VaR &amp; ES'!C8</f>
         <v/>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="16">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="16">
         <f>D5-C5</f>
         <v/>
       </c>
-      <c r="F5" s="28">
+      <c r="F5">
         <f>IF(C5&lt;=D5,"PASS","BREACH")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Worst stress loss</t>
         </is>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="16">
         <f>-MIN(Stress!I5:I10)</f>
         <v/>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="16">
         <f>Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="16">
         <f>D6-C6</f>
         <v/>
       </c>
-      <c r="F6" s="28">
+      <c r="F6">
         <f>IF(C6&lt;=D6,"PASS","BREACH")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Illiquid NAV</t>
         </is>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="14">
         <f>Liquidity!C20</f>
         <v/>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="14">
         <f>Assumptions!E14</f>
         <v/>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="14">
         <f>D7-C7</f>
         <v/>
       </c>
-      <c r="F7" s="28">
+      <c r="F7">
         <f>IF(C7&lt;=D7,"PASS","BREACH")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Single-name concentration</t>
         </is>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="14">
         <f>MAX(ABS(Positions!D5:D16))/Assumptions!E18</f>
         <v/>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="14">
         <f>Assumptions!E15</f>
         <v/>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="14">
         <f>D8-C8</f>
         <v/>
       </c>
-      <c r="F8" s="28">
+      <c r="F8">
         <f>IF(C8&lt;=D8,"PASS","BREACH")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gross leverage</t>
         </is>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="18">
         <f>SUM(ABS(Positions!E5:E16))/Assumptions!E18</f>
         <v/>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="18">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="18">
         <f>D9-C9</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9">
         <f>IF(C9&lt;=D9,"PASS","BREACH")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Unexplained P&amp;L</t>
         </is>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="16">
         <f>ABS('P&amp;L Explain'!G14)</f>
         <v/>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="16">
         <f>D10-C10</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10">
         <f>IF(C10&lt;=D10,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -1986,153 +1918,151 @@
     <mergeCell ref="B2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F10">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>F5="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>F5="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>F5="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="44" customWidth="1" style="28" min="2" max="2"/>
-    <col width="18" customWidth="1" style="28" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Risk Model Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Correlation diagonal equals one</t>
         </is>
       </c>
-      <c r="C5" s="28">
+      <c r="C5">
         <f>IF(AND(Factors!E5=1,Factors!F6=1,Factors!G7=1,Factors!H8=1,Factors!I9=1),"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Correlation matrix bounded</t>
         </is>
       </c>
-      <c r="C6" s="28">
+      <c r="C6">
         <f>IF(AND(MIN(Factors!E5:I9)&gt;=-1,MAX(Factors!E5:I9)&lt;=1),"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Portfolio variance nonnegative</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7">
         <f>IF(Factors!C12&gt;=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>VaR and ES positive</t>
         </is>
       </c>
-      <c r="C8" s="28">
+      <c r="C8">
         <f>IF(AND('VaR &amp; ES'!C8&gt;=0,'VaR &amp; ES'!C9&gt;='VaR &amp; ES'!C8),"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>No risk limit breaches</t>
         </is>
       </c>
-      <c r="C9" s="28">
+      <c r="C9">
         <f>IF(COUNTIF(Limits!F5:F10,"BREACH")=0,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Liquidity loss nonnegative</t>
         </is>
       </c>
-      <c r="C10" s="28">
+      <c r="C10">
         <f>IF(Liquidity!C21&gt;=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="B11" s="28" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Position inventory populated</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11">
         <f>IF(COUNTA(Positions!B5:B16)=12,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="28" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>P&amp;L explain complete</t>
         </is>
       </c>
-      <c r="C12" s="28">
+      <c r="C12">
         <f>IF(COUNT('P&amp;L Explain'!G5:G9)=5,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="28" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="C13" s="28">
+      <c r="C13">
         <f>IF(COUNTIF(C5:C12,"FAIL")=0,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -2142,175 +2072,173 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C13">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C5="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C5="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C5="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="34" customWidth="1" style="28" min="2" max="2"/>
-    <col width="58" customWidth="1" style="28" min="3" max="3"/>
-    <col width="16" customWidth="1" style="28" min="4" max="4"/>
-    <col width="48" customWidth="1" style="28" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Source Register</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Input / dataset</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Source URL or document</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes / transformation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="59" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Position and market-value feed</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>[OMS / risk source]</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Reconcile to books and records</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="59" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Factor and covariance calibration</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>[model dataset URL]</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>[window]</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Document decay, winsorization, and regime treatment</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="59" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Curve, spread, volatility, and FX data</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>[market data URL]</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Record interpolation and stale-data policy</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="59" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Liquidity and ADV data</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>[venue / vendor source]</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>[period]</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Document liquidation horizon and impact calibration</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="59" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Risk limit policy</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>[approved policy URL]</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>[effective date]</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Thresholds, escalation, exceptions, and ownership</t>
         </is>
@@ -2320,276 +2248,272 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="14" customWidth="1" style="28" min="2" max="2"/>
-    <col width="22" customWidth="1" style="28" min="3" max="3"/>
-    <col width="28" customWidth="1" style="28" min="4" max="4"/>
-    <col width="38" customWidth="1" style="28" min="5" max="5"/>
-    <col width="34" customWidth="1" style="28" min="6" max="6"/>
-    <col width="18" customWidth="1" style="28" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refresh Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Source snapshot</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Reviewer / challenge</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Next check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="60" t="n"/>
-      <c r="C5" s="60" t="n"/>
-      <c r="D5" s="60" t="n"/>
-      <c r="E5" s="60" t="n"/>
-      <c r="F5" s="60" t="n"/>
-      <c r="G5" s="60" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="60" t="n"/>
-      <c r="C6" s="60" t="n"/>
-      <c r="D6" s="60" t="n"/>
-      <c r="E6" s="60" t="n"/>
-      <c r="F6" s="60" t="n"/>
-      <c r="G6" s="60" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="60" t="n"/>
-      <c r="C7" s="60" t="n"/>
-      <c r="D7" s="60" t="n"/>
-      <c r="E7" s="60" t="n"/>
-      <c r="F7" s="60" t="n"/>
-      <c r="G7" s="60" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="60" t="n"/>
-      <c r="C9" s="60" t="n"/>
-      <c r="D9" s="60" t="n"/>
-      <c r="E9" s="60" t="n"/>
-      <c r="F9" s="60" t="n"/>
-      <c r="G9" s="60" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="60" t="n"/>
-      <c r="C10" s="60" t="n"/>
-      <c r="D10" s="60" t="n"/>
-      <c r="E10" s="60" t="n"/>
-      <c r="F10" s="60" t="n"/>
-      <c r="G10" s="60" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="B11" s="60" t="n"/>
-      <c r="C11" s="60" t="n"/>
-      <c r="D11" s="60" t="n"/>
-      <c r="E11" s="60" t="n"/>
-      <c r="F11" s="60" t="n"/>
-      <c r="G11" s="60" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="60" t="n"/>
-      <c r="C12" s="60" t="n"/>
-      <c r="D12" s="60" t="n"/>
-      <c r="E12" s="60" t="n"/>
-      <c r="F12" s="60" t="n"/>
-      <c r="G12" s="60" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="60" t="n"/>
-      <c r="C13" s="60" t="n"/>
-      <c r="D13" s="60" t="n"/>
-      <c r="E13" s="60" t="n"/>
-      <c r="F13" s="60" t="n"/>
-      <c r="G13" s="60" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="B14" s="60" t="n"/>
-      <c r="C14" s="60" t="n"/>
-      <c r="D14" s="60" t="n"/>
-      <c r="E14" s="60" t="n"/>
-      <c r="F14" s="60" t="n"/>
-      <c r="G14" s="60" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="29">
-      <c r="B15" s="60" t="n"/>
-      <c r="C15" s="60" t="n"/>
-      <c r="D15" s="60" t="n"/>
-      <c r="E15" s="60" t="n"/>
-      <c r="F15" s="60" t="n"/>
-      <c r="G15" s="60" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="29">
-      <c r="B16" s="60" t="n"/>
-      <c r="C16" s="60" t="n"/>
-      <c r="D16" s="60" t="n"/>
-      <c r="E16" s="60" t="n"/>
-      <c r="F16" s="60" t="n"/>
-      <c r="G16" s="60" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="29">
-      <c r="B17" s="60" t="n"/>
-      <c r="C17" s="60" t="n"/>
-      <c r="D17" s="60" t="n"/>
-      <c r="E17" s="60" t="n"/>
-      <c r="F17" s="60" t="n"/>
-      <c r="G17" s="60" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="29">
-      <c r="B18" s="60" t="n"/>
-      <c r="C18" s="60" t="n"/>
-      <c r="D18" s="60" t="n"/>
-      <c r="E18" s="60" t="n"/>
-      <c r="F18" s="60" t="n"/>
-      <c r="G18" s="60" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="29">
-      <c r="B19" s="60" t="n"/>
-      <c r="C19" s="60" t="n"/>
-      <c r="D19" s="60" t="n"/>
-      <c r="E19" s="60" t="n"/>
-      <c r="F19" s="60" t="n"/>
-      <c r="G19" s="60" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="29">
-      <c r="B20" s="60" t="n"/>
-      <c r="C20" s="60" t="n"/>
-      <c r="D20" s="60" t="n"/>
-      <c r="E20" s="60" t="n"/>
-      <c r="F20" s="60" t="n"/>
-      <c r="G20" s="60" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="29">
-      <c r="B21" s="60" t="n"/>
-      <c r="C21" s="60" t="n"/>
-      <c r="D21" s="60" t="n"/>
-      <c r="E21" s="60" t="n"/>
-      <c r="F21" s="60" t="n"/>
-      <c r="G21" s="60" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="29">
-      <c r="B22" s="60" t="n"/>
-      <c r="C22" s="60" t="n"/>
-      <c r="D22" s="60" t="n"/>
-      <c r="E22" s="60" t="n"/>
-      <c r="F22" s="60" t="n"/>
-      <c r="G22" s="60" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="29">
-      <c r="B23" s="60" t="n"/>
-      <c r="C23" s="60" t="n"/>
-      <c r="D23" s="60" t="n"/>
-      <c r="E23" s="60" t="n"/>
-      <c r="F23" s="60" t="n"/>
-      <c r="G23" s="60" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="29">
-      <c r="B24" s="60" t="n"/>
-      <c r="C24" s="60" t="n"/>
-      <c r="D24" s="60" t="n"/>
-      <c r="E24" s="60" t="n"/>
-      <c r="F24" s="60" t="n"/>
-      <c r="G24" s="60" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="29">
-      <c r="B25" s="60" t="n"/>
-      <c r="C25" s="60" t="n"/>
-      <c r="D25" s="60" t="n"/>
-      <c r="E25" s="60" t="n"/>
-      <c r="F25" s="60" t="n"/>
-      <c r="G25" s="60" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="29">
-      <c r="B26" s="60" t="n"/>
-      <c r="C26" s="60" t="n"/>
-      <c r="D26" s="60" t="n"/>
-      <c r="E26" s="60" t="n"/>
-      <c r="F26" s="60" t="n"/>
-      <c r="G26" s="60" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="29">
-      <c r="B27" s="60" t="n"/>
-      <c r="C27" s="60" t="n"/>
-      <c r="D27" s="60" t="n"/>
-      <c r="E27" s="60" t="n"/>
-      <c r="F27" s="60" t="n"/>
-      <c r="G27" s="60" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="29">
-      <c r="B28" s="60" t="n"/>
-      <c r="C28" s="60" t="n"/>
-      <c r="D28" s="60" t="n"/>
-      <c r="E28" s="60" t="n"/>
-      <c r="F28" s="60" t="n"/>
-      <c r="G28" s="60" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="29">
-      <c r="B29" s="60" t="n"/>
-      <c r="C29" s="60" t="n"/>
-      <c r="D29" s="60" t="n"/>
-      <c r="E29" s="60" t="n"/>
-      <c r="F29" s="60" t="n"/>
-      <c r="G29" s="60" t="n"/>
+    <row r="5">
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="24" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="24" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2602,133 +2526,133 @@
   <dimension ref="B2:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="29" min="2" max="2"/>
-    <col width="48" customWidth="1" style="29" min="3" max="3"/>
-    <col width="24" customWidth="1" style="29" min="4" max="4"/>
-    <col width="34" customWidth="1" style="29" min="5" max="5"/>
-    <col width="20" customWidth="1" style="29" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Risk Management — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Risk Management</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>tools/builders/build_risk_release.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>trading desk, independent risk, model validation, senior risk committee and regulator</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>daily risk and limit pack</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>intraday monitoring; daily sign-off; monthly committee</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="41" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="41" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="41" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="41" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2820,34 +2744,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="41" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="41" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="41" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="41" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2939,34 +2863,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="41" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="41" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="41" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="41" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3058,34 +2982,34 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="41" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="41" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="41" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="41" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="41" t="inlineStr">
+      <c r="F37" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3177,34 +3101,34 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="40" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="41" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="41" t="inlineStr">
+      <c r="D45" s="30" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="41" t="inlineStr">
+      <c r="E45" s="30" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="41" t="inlineStr">
+      <c r="F45" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3296,34 +3220,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="40" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="41" t="inlineStr">
+      <c r="B53" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="41" t="inlineStr">
+      <c r="C53" s="30" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="41" t="inlineStr">
+      <c r="D53" s="30" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="41" t="inlineStr">
+      <c r="E53" s="30" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="41" t="inlineStr">
+      <c r="F53" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3415,34 +3339,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="40" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="41" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="41" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="41" t="inlineStr">
+      <c r="D61" s="30" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="41" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="41" t="inlineStr">
+      <c r="F61" s="30" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
@@ -3568,60 +3492,60 @@
   <dimension ref="B2:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="29" min="2" max="2"/>
-    <col width="22" customWidth="1" style="29" min="3" max="3"/>
-    <col width="52" customWidth="1" style="29" min="4" max="4"/>
-    <col width="46" customWidth="1" style="29" min="5" max="5"/>
-    <col width="36" customWidth="1" style="29" min="6" max="6"/>
-    <col width="14" customWidth="1" style="29" min="7" max="7"/>
-    <col width="18" customWidth="1" style="29" min="8" max="8"/>
-    <col width="14" customWidth="1" style="29" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="41" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="41" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="41" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
@@ -3742,66 +3666,66 @@
   <dimension ref="B2:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="29" min="2" max="2"/>
-    <col width="18" customWidth="1" style="29" min="3" max="3"/>
-    <col width="42" customWidth="1" style="29" min="4" max="4"/>
-    <col width="24" customWidth="1" style="29" min="5" max="5"/>
-    <col width="18" customWidth="1" style="29" min="6" max="6"/>
-    <col width="22" customWidth="1" style="29" min="7" max="7"/>
-    <col width="42" customWidth="1" style="29" min="8" max="8"/>
-    <col width="30" customWidth="1" style="29" min="9" max="9"/>
-    <col width="15" customWidth="1" style="29" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="41" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="41" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="41" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="41" t="inlineStr">
+      <c r="J4" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3930,356 +3854,358 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="40" customWidth="1" style="28" min="2" max="2"/>
-    <col width="15" customWidth="1" style="28" min="3" max="5"/>
-    <col width="30" customWidth="1" style="28" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Risk and Liquidity Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Units / note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>VaR confidence</t>
         </is>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="9" t="n">
         <v>0.99</v>
       </c>
-      <c r="D5" s="43" t="n">
+      <c r="D5" s="9" t="n">
         <v>0.995</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="10">
         <f>IF(Cover!$C$9="Downside",D5,C5)</f>
         <v/>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Trading days per year</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n">
+      <c r="C6" s="11" t="n">
         <v>252</v>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D6" s="11" t="n">
         <v>252</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="12">
         <f>IF(Cover!$C$9="Downside",D6,C6)</f>
         <v/>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Equity annual volatility</t>
         </is>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.22</v>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="9" t="n">
         <v>0.35</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="10">
         <f>IF(Cover!$C$9="Downside",D7,C7)</f>
         <v/>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Rates annual volatility</t>
         </is>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="13" t="n">
         <v>0.012</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="14">
         <f>IF(Cover!$C$9="Downside",D8,C8)</f>
         <v/>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>yield change</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Credit annual volatility</t>
         </is>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="13" t="n">
         <v>0.015</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="13" t="n">
         <v>0.035</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="14">
         <f>IF(Cover!$C$9="Downside",D9,C9)</f>
         <v/>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>spread change</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>FX annual volatility</t>
         </is>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C10" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="10">
         <f>IF(Cover!$C$9="Downside",D10,C10)</f>
         <v/>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="B11" s="28" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Volatility-factor annual volatility</t>
         </is>
       </c>
-      <c r="C11" s="43" t="n">
+      <c r="C11" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="10">
         <f>IF(Cover!$C$9="Downside",D11,C11)</f>
         <v/>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="28" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Maximum portfolio VaR</t>
         </is>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="16">
         <f>IF(Cover!$C$9="Downside",D12,C12)</f>
         <v/>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="28" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Maximum stress loss</t>
         </is>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="16">
         <f>IF(Cover!$C$9="Downside",D13,C13)</f>
         <v/>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="B14" s="28" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Maximum illiquid NAV</t>
         </is>
       </c>
-      <c r="C14" s="43" t="n">
+      <c r="C14" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="10">
         <f>IF(Cover!$C$9="Downside",D14,C14)</f>
         <v/>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="29">
-      <c r="B15" s="28" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Maximum single-name concentration</t>
         </is>
       </c>
-      <c r="C15" s="43" t="n">
+      <c r="C15" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="D15" s="43" t="n">
+      <c r="D15" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="10">
         <f>IF(Cover!$C$9="Downside",D15,C15)</f>
         <v/>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="29">
-      <c r="B16" s="28" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Maximum gross leverage</t>
         </is>
       </c>
-      <c r="C16" s="51" t="n">
+      <c r="C16" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="51" t="n">
+      <c r="D16" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="52">
+      <c r="E16" s="18">
         <f>IF(Cover!$C$9="Downside",D16,C16)</f>
         <v/>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="29">
-      <c r="B17" s="28" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Liquidity impact coefficient</t>
         </is>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="13" t="n">
         <v>0.015</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="14">
         <f>IF(Cover!$C$9="Downside",D17,C17)</f>
         <v/>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>loss coefficient</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="29">
-      <c r="B18" s="28" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Available capital / NAV</t>
         </is>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="16">
         <f>IF(Cover!$C$9="Downside",D18,C18)</f>
         <v/>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
@@ -4289,896 +4215,909 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:S18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="28" customWidth="1" style="28" min="2" max="2"/>
-    <col width="16" customWidth="1" style="28" min="3" max="3"/>
-    <col width="13" customWidth="1" style="28" min="4" max="19"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Position-Level Risk Inventory</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="23.85" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Asset class</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Market value</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Gross notional</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="I4" s="42" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Spread duration</t>
         </is>
       </c>
-      <c r="J4" s="42" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>DV01</t>
         </is>
       </c>
-      <c r="K4" s="42" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Vega</t>
         </is>
       </c>
-      <c r="L4" s="42" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>FX delta</t>
         </is>
       </c>
-      <c r="M4" s="42" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Days to liquidate</t>
         </is>
       </c>
-      <c r="N4" s="42" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="O4" s="42" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="P4" s="42" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="Q4" s="42" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="R4" s="42" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="S4" s="42" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Weighted risk exposure</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Equity Index Future</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="15" t="n">
         <v>120</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="F5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="47" t="n">
+      <c r="G5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="53" t="n">
+      <c r="H5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="N5" s="47" t="n">
+      <c r="N5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="50">
+      <c r="O5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="16">
         <f>SUMPRODUCT(C5:Q5,C5:Q5)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Single Name A</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="H6" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="53" t="n">
+      <c r="H6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="47" t="n">
+      <c r="N6" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="O6" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="47" t="n">
+      <c r="O6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="47" t="n">
+      <c r="Q6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="16">
         <f>SUMPRODUCT(C6:Q6,C6:Q6)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Single Name Put</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="13" t="n">
         <v>-0.35</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="13" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H7" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="49" t="n">
+      <c r="H7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="15" t="n">
         <v>0.18</v>
       </c>
-      <c r="L7" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="53" t="n">
+      <c r="L7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="N7" s="47" t="n">
+      <c r="N7" s="13" t="n">
         <v>-0.4</v>
       </c>
-      <c r="O7" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="47" t="n">
+      <c r="O7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13" t="n">
         <v>0.8</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="16">
         <f>SUMPRODUCT(C7:Q7,C7:Q7)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>10Y Treasury</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="49" t="n">
+      <c r="E8" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="53" t="n">
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I8" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="49" t="n">
+      <c r="I8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="15" t="n">
         <v>0.041</v>
       </c>
-      <c r="K8" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="53" t="n">
+      <c r="K8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N8" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="47" t="n">
+      <c r="N8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="13" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="P8" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="50">
+      <c r="P8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="16">
         <f>SUMPRODUCT(C8:Q8,C8:Q8)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>IG Credit ETF</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.35</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="19" t="n">
         <v>5.5</v>
       </c>
-      <c r="I9" s="53" t="n">
+      <c r="I9" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="15" t="n">
         <v>0.018</v>
       </c>
-      <c r="K9" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="53" t="n">
+      <c r="K9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="47" t="n">
+      <c r="N9" s="13" t="n">
         <v>0.35</v>
       </c>
-      <c r="O9" s="47" t="n">
+      <c r="O9" s="13" t="n">
         <v>-2</v>
       </c>
-      <c r="P9" s="47" t="n">
+      <c r="P9" s="13" t="n">
         <v>-5</v>
       </c>
-      <c r="Q9" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="50">
+      <c r="Q9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="16">
         <f>SUMPRODUCT(C9:Q9,C9:Q9)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>HY Bond</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.55</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="53" t="n">
+      <c r="I10" s="19" t="n">
         <v>3.8</v>
       </c>
-      <c r="J10" s="49" t="n">
+      <c r="J10" s="15" t="n">
         <v>0.011</v>
       </c>
-      <c r="K10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="53" t="n">
+      <c r="K10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="47" t="n">
+      <c r="N10" s="13" t="n">
         <v>0.55</v>
       </c>
-      <c r="O10" s="47" t="n">
+      <c r="O10" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="P10" s="47" t="n">
+      <c r="P10" s="13" t="n">
         <v>-3.8</v>
       </c>
-      <c r="Q10" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="50">
+      <c r="Q10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="16">
         <f>SUMPRODUCT(C10:Q10,C10:Q10)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="B11" s="28" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>EURUSD Forward</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="49" t="n">
+      <c r="G11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="M11" s="53" t="n">
+      <c r="M11" s="19" t="n">
         <v>0.3</v>
       </c>
-      <c r="N11" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="47" t="n">
+      <c r="N11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="50">
+      <c r="R11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="16">
         <f>SUMPRODUCT(C11:Q11,C11:Q11)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="28" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Commodity Future</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Commodity</t>
         </is>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="15" t="n">
         <v>65</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="H12" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="53" t="n">
+      <c r="H12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N12" s="47" t="n">
+      <c r="N12" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="O12" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="47" t="n">
+      <c r="O12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q12" s="47" t="n">
+      <c r="Q12" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="R12" s="47" t="n">
+      <c r="R12" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="16">
         <f>SUMPRODUCT(C12:Q12,C12:Q12)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="28" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Variance Swap</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="49" t="n">
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="15" t="n">
         <v>0.45</v>
       </c>
-      <c r="L13" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="53" t="n">
+      <c r="L13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="N13" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="47" t="n">
+      <c r="N13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" s="50">
+      <c r="S13" s="16">
         <f>SUMPRODUCT(C13:Q13,C13:Q13)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="B14" s="28" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Private Credit Position</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Private</t>
         </is>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="F14" s="47" t="n">
+      <c r="F14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="H14" s="53" t="n">
+      <c r="H14" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="53" t="n">
+      <c r="I14" s="19" t="n">
         <v>2.5</v>
       </c>
-      <c r="J14" s="49" t="n">
+      <c r="J14" s="15" t="n">
         <v>0.008</v>
       </c>
-      <c r="K14" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="53" t="n">
+      <c r="K14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="N14" s="47" t="n">
+      <c r="N14" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="O14" s="47" t="n">
+      <c r="O14" s="13" t="n">
         <v>-0.5</v>
       </c>
-      <c r="P14" s="47" t="n">
+      <c r="P14" s="13" t="n">
         <v>-2.5</v>
       </c>
-      <c r="Q14" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="50">
+      <c r="Q14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="16">
         <f>SUMPRODUCT(C14:Q14,C14:Q14)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="29">
-      <c r="B15" s="28" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="50">
+      <c r="G15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="16">
         <f>SUMPRODUCT(C15:Q15,C15:Q15)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="29">
-      <c r="B16" s="28" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Short Equity Basket</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="15" t="n">
         <v>-18</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="13" t="n">
         <v>-1</v>
       </c>
-      <c r="G16" s="47" t="n">
+      <c r="G16" s="13" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H16" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="53" t="n">
+      <c r="H16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="N16" s="47" t="n">
+      <c r="N16" s="13" t="n">
         <v>-0.9</v>
       </c>
-      <c r="O16" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="47" t="n">
+      <c r="O16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13" t="n">
         <v>-0.1</v>
       </c>
-      <c r="Q16" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="50">
+      <c r="Q16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="16">
         <f>SUMPRODUCT(C16:Q16,C16:Q16)^0.5</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="29">
-      <c r="B18" s="54" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Portfolio total</t>
         </is>
       </c>
-      <c r="C18" s="54" t="n"/>
-      <c r="D18" s="55">
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="21">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="21">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F18" s="54" t="n"/>
-      <c r="G18" s="54" t="n"/>
-      <c r="H18" s="54" t="n"/>
-      <c r="I18" s="54" t="n"/>
-      <c r="J18" s="55">
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="21">
         <f>SUM(J5:J16)</f>
         <v/>
       </c>
-      <c r="K18" s="55">
+      <c r="K18" s="21">
         <f>SUM(K5:K16)</f>
         <v/>
       </c>
-      <c r="L18" s="55">
+      <c r="L18" s="21">
         <f>SUM(L5:L16)</f>
         <v/>
       </c>
-      <c r="M18" s="54" t="n"/>
-      <c r="N18" s="54" t="n"/>
-      <c r="O18" s="54" t="n"/>
-      <c r="P18" s="54" t="n"/>
-      <c r="Q18" s="54" t="n"/>
-      <c r="R18" s="54" t="n"/>
-      <c r="S18" s="55">
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="20" t="n"/>
+      <c r="O18" s="20" t="n"/>
+      <c r="P18" s="20" t="n"/>
+      <c r="Q18" s="20" t="n"/>
+      <c r="R18" s="20" t="n"/>
+      <c r="S18" s="21">
         <f>SUM(S5:S16)</f>
         <v/>
       </c>
@@ -5187,245 +5126,247 @@
   <mergeCells count="1">
     <mergeCell ref="B2:S2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="20" customWidth="1" style="28" min="2" max="2"/>
-    <col width="18" customWidth="1" style="28" min="3" max="3"/>
-    <col width="16" customWidth="1" style="28" min="4" max="4"/>
-    <col width="12" customWidth="1" style="28" min="5" max="9"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Factor Exposure and Covariance</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Annual vol</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="I4" s="42" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="16">
         <f>SUMPRODUCT(Positions!$D$5:$D$16,Positions!$N$5:$N$16)</f>
         <v/>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="14">
         <f>Assumptions!E7</f>
         <v/>
       </c>
-      <c r="E5" s="53" t="n">
+      <c r="E5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G5" s="53" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.35</v>
       </c>
-      <c r="H5" s="53" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I5" s="53" t="n">
+      <c r="I5" s="19" t="n">
         <v>0.45</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="16">
         <f>SUMPRODUCT(Positions!$D$5:$D$16,Positions!$O$5:$O$16)</f>
         <v/>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="14">
         <f>Assumptions!E8</f>
         <v/>
       </c>
-      <c r="E6" s="53" t="n">
+      <c r="E6" s="19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="19" t="n">
         <v>-0.25</v>
       </c>
-      <c r="H6" s="53" t="n">
+      <c r="H6" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="I6" s="53" t="n">
+      <c r="I6" s="19" t="n">
         <v>-0.1</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="16">
         <f>SUMPRODUCT(Positions!$D$5:$D$16,Positions!$P$5:$P$16)</f>
         <v/>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="14">
         <f>Assumptions!E9</f>
         <v/>
       </c>
-      <c r="E7" s="53" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.35</v>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="19" t="n">
         <v>-0.25</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I7" s="53" t="n">
+      <c r="I7" s="19" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="16">
         <f>SUMPRODUCT(Positions!$D$5:$D$16,Positions!$Q$5:$Q$16)</f>
         <v/>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="14">
         <f>Assumptions!E10</f>
         <v/>
       </c>
-      <c r="E8" s="53" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="53" t="n">
+      <c r="I8" s="19" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="16">
         <f>SUMPRODUCT(Positions!$D$5:$D$16,Positions!$R$5:$R$16)</f>
         <v/>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="14">
         <f>Assumptions!E11</f>
         <v/>
       </c>
-      <c r="E9" s="53" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="19" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.3</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I9" s="53" t="n">
+      <c r="I9" s="19" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="28" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Annual portfolio variance</t>
         </is>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="16">
         <f>$C$5*$C$5*$D$5*$D$5*E5+$C$5*$C$6*$D$5*$D$6*F5+$C$5*$C$7*$D$5*$D$7*G5+$C$5*$C$8*$D$5*$D$8*H5+$C$5*$C$9*$D$5*$D$9*I5+$C$6*$C$5*$D$6*$D$5*E6+$C$6*$C$6*$D$6*$D$6*F6+$C$6*$C$7*$D$6*$D$7*G6+$C$6*$C$8*$D$6*$D$8*H6+$C$6*$C$9*$D$6*$D$9*I6+$C$7*$C$5*$D$7*$D$5*E7+$C$7*$C$6*$D$7*$D$6*F7+$C$7*$C$7*$D$7*$D$7*G7+$C$7*$C$8*$D$7*$D$8*H7+$C$7*$C$9*$D$7*$D$9*I7+$C$8*$C$5*$D$8*$D$5*E8+$C$8*$C$6*$D$8*$D$6*F8+$C$8*$C$7*$D$8*$D$7*G8+$C$8*$C$8*$D$8*$D$8*H8+$C$8*$C$9*$D$8*$D$9*I8+$C$9*$C$5*$D$9*$D$5*E9+$C$9*$C$6*$D$9*$D$6*F9+$C$9*$C$7*$D$9*$D$7*G9+$C$9*$C$8*$D$9*$D$8*H9+$C$9*$C$9*$D$9*$D$9*I9</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="28" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Annual portfolio volatility</t>
         </is>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="16">
         <f>SQRT(MAX(0,C12))</f>
         <v/>
       </c>
@@ -5434,199 +5375,197 @@
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="30" customWidth="1" style="28" min="2" max="2"/>
-    <col width="18" customWidth="1" style="28" min="3" max="3"/>
-    <col width="14" customWidth="1" style="28" min="4" max="4"/>
-    <col width="42" customWidth="1" style="28" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Parametric VaR and Expected Shortfall</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Annual portfolio volatility</t>
         </is>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="16">
         <f>Factors!C13</f>
         <v/>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>factor covariance</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Daily portfolio volatility</t>
         </is>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="16">
         <f>C5/SQRT(Assumptions!E6)</f>
         <v/>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>annual / sqrt(days)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Normal quantile</t>
         </is>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="22">
         <f>-NORMSINV(1-Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>confidence quantile</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>One-day VaR</t>
         </is>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="16">
         <f>C6*C7</f>
         <v/>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>sigma x z</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>One-day expected shortfall</t>
         </is>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="16">
         <f>C6*(EXP(-((C7)^2)/2)/SQRT(2*PI()))/(1-Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>normal tail expectation</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>VaR / NAV</t>
         </is>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="14">
         <f>C8/Assumptions!E18</f>
         <v/>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>capital consumption</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="B11" s="28" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Diversification benefit</t>
         </is>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="14">
         <f>1-C5/SUMPRODUCT(ABS(Factors!C5:C9),Factors!D5:D9)</f>
         <v/>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1 - portfolio / standalone</t>
         </is>
@@ -5636,612 +5575,613 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:J22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="28" min="1" max="1"/>
-    <col width="28" customWidth="1" style="28" min="2" max="2"/>
-    <col width="16" customWidth="1" style="28" min="3" max="6"/>
-    <col width="18" customWidth="1" style="28" min="7" max="7"/>
-    <col width="16" customWidth="1" style="28" min="8" max="8"/>
-    <col width="20" customWidth="1" style="28" min="9" max="9"/>
-    <col width="18" customWidth="1" style="28" min="10" max="10"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="29">
-      <c r="B2" s="30" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Position-Level VaR, Stress, and Liquidity Contributions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="29">
-      <c r="B4" s="42" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Gross notional</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Standalone VaR</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Component VaR</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>% portfolio VaR</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Worst stress loss</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Liquidation loss</t>
         </is>
       </c>
-      <c r="I4" s="42" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Liquidity-adjusted risk</t>
         </is>
       </c>
-      <c r="J4" s="42" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Risk concentration</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="29">
-      <c r="B5" s="28">
+    <row r="5">
+      <c r="B5">
         <f>Positions!B5</f>
         <v/>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="16">
         <f>ABS(Positions!E5)</f>
         <v/>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$5*Positions!$N$5)*(Positions!$E$5*Positions!$N$5)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$5*Positions!$N$5)*(Positions!$E$5*Positions!$O$5)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$5*Positions!$N$5)*(Positions!$E$5*Positions!$P$5)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$5*Positions!$N$5)*(Positions!$E$5*Positions!$Q$5)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$5*Positions!$N$5)*(Positions!$E$5*Positions!$R$5)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$5*Positions!$O$5)*(Positions!$E$5*Positions!$N$5)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$5*Positions!$O$5)*(Positions!$E$5*Positions!$O$5)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$5*Positions!$O$5)*(Positions!$E$5*Positions!$P$5)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$5*Positions!$O$5)*(Positions!$E$5*Positions!$Q$5)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$5*Positions!$O$5)*(Positions!$E$5*Positions!$R$5)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$5*Positions!$P$5)*(Positions!$E$5*Positions!$N$5)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$5*Positions!$P$5)*(Positions!$E$5*Positions!$O$5)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$5*Positions!$P$5)*(Positions!$E$5*Positions!$P$5)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$5*Positions!$P$5)*(Positions!$E$5*Positions!$Q$5)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$5*Positions!$P$5)*(Positions!$E$5*Positions!$R$5)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$5*Positions!$Q$5)*(Positions!$E$5*Positions!$N$5)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$5*Positions!$Q$5)*(Positions!$E$5*Positions!$O$5)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$5*Positions!$Q$5)*(Positions!$E$5*Positions!$P$5)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$5*Positions!$Q$5)*(Positions!$E$5*Positions!$Q$5)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$5*Positions!$Q$5)*(Positions!$E$5*Positions!$R$5)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$5*Positions!$R$5)*(Positions!$E$5*Positions!$N$5)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$5*Positions!$R$5)*(Positions!$E$5*Positions!$O$5)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$5*Positions!$R$5)*(Positions!$E$5*Positions!$P$5)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$5*Positions!$R$5)*(Positions!$E$5*Positions!$Q$5)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$5*Positions!$R$5)*(Positions!$E$5*Positions!$R$5)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$5*Positions!$N$5)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$5*Positions!$N$5)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$5*Positions!$N$5)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$5*Positions!$N$5)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$5*Positions!$N$5)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$5*Positions!$O$5)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$5*Positions!$O$5)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$5*Positions!$O$5)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$5*Positions!$O$5)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$5*Positions!$O$5)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$5*Positions!$P$5)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$5*Positions!$P$5)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$5*Positions!$P$5)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$5*Positions!$P$5)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$5*Positions!$P$5)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$5*Positions!$Q$5)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$5*Positions!$Q$5)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$5*Positions!$Q$5)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$5*Positions!$Q$5)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$5*Positions!$Q$5)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$5*Positions!$R$5)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$5*Positions!$R$5)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$5*Positions!$R$5)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$5*Positions!$R$5)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$5*Positions!$R$5)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="14">
         <f>IFERROR(E5/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="16">
         <f>-MIN((Positions!$E$5*Positions!$N$5*Stress!$C$5+Positions!$E$5*Positions!$O$5*Stress!$D$5+Positions!$E$5*Positions!$P$5*Stress!$E$5+Positions!$E$5*Positions!$Q$5*Stress!$F$5+Positions!$E$5*Positions!$R$5*Stress!$G$5),(Positions!$E$5*Positions!$N$5*Stress!$C$6+Positions!$E$5*Positions!$O$5*Stress!$D$6+Positions!$E$5*Positions!$P$5*Stress!$E$6+Positions!$E$5*Positions!$Q$5*Stress!$F$6+Positions!$E$5*Positions!$R$5*Stress!$G$6),(Positions!$E$5*Positions!$N$5*Stress!$C$7+Positions!$E$5*Positions!$O$5*Stress!$D$7+Positions!$E$5*Positions!$P$5*Stress!$E$7+Positions!$E$5*Positions!$Q$5*Stress!$F$7+Positions!$E$5*Positions!$R$5*Stress!$G$7),(Positions!$E$5*Positions!$N$5*Stress!$C$8+Positions!$E$5*Positions!$O$5*Stress!$D$8+Positions!$E$5*Positions!$P$5*Stress!$E$8+Positions!$E$5*Positions!$Q$5*Stress!$F$8+Positions!$E$5*Positions!$R$5*Stress!$G$8),(Positions!$E$5*Positions!$N$5*Stress!$C$9+Positions!$E$5*Positions!$O$5*Stress!$D$9+Positions!$E$5*Positions!$P$5*Stress!$E$9+Positions!$E$5*Positions!$Q$5*Stress!$F$9+Positions!$E$5*Positions!$R$5*Stress!$G$9),(Positions!$E$5*Positions!$N$5*Stress!$C$10+Positions!$E$5*Positions!$O$5*Stress!$D$10+Positions!$E$5*Positions!$P$5*Stress!$E$10+Positions!$E$5*Positions!$Q$5*Stress!$F$10+Positions!$E$5*Positions!$R$5*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="16">
         <f>Liquidity!G5</f>
         <v/>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="16">
         <f>ABS(E5)+G5+H5</f>
         <v/>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="14">
         <f>IFERROR(I5/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="29">
-      <c r="B6" s="28">
+    <row r="6">
+      <c r="B6">
         <f>Positions!B6</f>
         <v/>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="16">
         <f>ABS(Positions!E6)</f>
         <v/>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$6*Positions!$N$6)*(Positions!$E$6*Positions!$N$6)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$6*Positions!$N$6)*(Positions!$E$6*Positions!$O$6)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$6*Positions!$N$6)*(Positions!$E$6*Positions!$P$6)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$6*Positions!$N$6)*(Positions!$E$6*Positions!$Q$6)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$6*Positions!$N$6)*(Positions!$E$6*Positions!$R$6)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$6*Positions!$O$6)*(Positions!$E$6*Positions!$N$6)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$6*Positions!$O$6)*(Positions!$E$6*Positions!$O$6)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$6*Positions!$O$6)*(Positions!$E$6*Positions!$P$6)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$6*Positions!$O$6)*(Positions!$E$6*Positions!$Q$6)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$6*Positions!$O$6)*(Positions!$E$6*Positions!$R$6)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$6*Positions!$P$6)*(Positions!$E$6*Positions!$N$6)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$6*Positions!$P$6)*(Positions!$E$6*Positions!$O$6)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$6*Positions!$P$6)*(Positions!$E$6*Positions!$P$6)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$6*Positions!$P$6)*(Positions!$E$6*Positions!$Q$6)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$6*Positions!$P$6)*(Positions!$E$6*Positions!$R$6)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$6*Positions!$Q$6)*(Positions!$E$6*Positions!$N$6)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$6*Positions!$Q$6)*(Positions!$E$6*Positions!$O$6)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$6*Positions!$Q$6)*(Positions!$E$6*Positions!$P$6)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$6*Positions!$Q$6)*(Positions!$E$6*Positions!$Q$6)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$6*Positions!$Q$6)*(Positions!$E$6*Positions!$R$6)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$6*Positions!$R$6)*(Positions!$E$6*Positions!$N$6)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$6*Positions!$R$6)*(Positions!$E$6*Positions!$O$6)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$6*Positions!$R$6)*(Positions!$E$6*Positions!$P$6)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$6*Positions!$R$6)*(Positions!$E$6*Positions!$Q$6)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$6*Positions!$R$6)*(Positions!$E$6*Positions!$R$6)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$6*Positions!$N$6)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$6*Positions!$N$6)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$6*Positions!$N$6)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$6*Positions!$N$6)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$6*Positions!$N$6)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$6*Positions!$O$6)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$6*Positions!$O$6)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$6*Positions!$O$6)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$6*Positions!$O$6)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$6*Positions!$O$6)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$6*Positions!$P$6)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$6*Positions!$P$6)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$6*Positions!$P$6)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$6*Positions!$P$6)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$6*Positions!$P$6)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$6*Positions!$Q$6)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$6*Positions!$Q$6)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$6*Positions!$Q$6)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$6*Positions!$Q$6)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$6*Positions!$Q$6)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$6*Positions!$R$6)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$6*Positions!$R$6)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$6*Positions!$R$6)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$6*Positions!$R$6)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$6*Positions!$R$6)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="14">
         <f>IFERROR(E6/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="16">
         <f>-MIN((Positions!$E$6*Positions!$N$6*Stress!$C$5+Positions!$E$6*Positions!$O$6*Stress!$D$5+Positions!$E$6*Positions!$P$6*Stress!$E$5+Positions!$E$6*Positions!$Q$6*Stress!$F$5+Positions!$E$6*Positions!$R$6*Stress!$G$5),(Positions!$E$6*Positions!$N$6*Stress!$C$6+Positions!$E$6*Positions!$O$6*Stress!$D$6+Positions!$E$6*Positions!$P$6*Stress!$E$6+Positions!$E$6*Positions!$Q$6*Stress!$F$6+Positions!$E$6*Positions!$R$6*Stress!$G$6),(Positions!$E$6*Positions!$N$6*Stress!$C$7+Positions!$E$6*Positions!$O$6*Stress!$D$7+Positions!$E$6*Positions!$P$6*Stress!$E$7+Positions!$E$6*Positions!$Q$6*Stress!$F$7+Positions!$E$6*Positions!$R$6*Stress!$G$7),(Positions!$E$6*Positions!$N$6*Stress!$C$8+Positions!$E$6*Positions!$O$6*Stress!$D$8+Positions!$E$6*Positions!$P$6*Stress!$E$8+Positions!$E$6*Positions!$Q$6*Stress!$F$8+Positions!$E$6*Positions!$R$6*Stress!$G$8),(Positions!$E$6*Positions!$N$6*Stress!$C$9+Positions!$E$6*Positions!$O$6*Stress!$D$9+Positions!$E$6*Positions!$P$6*Stress!$E$9+Positions!$E$6*Positions!$Q$6*Stress!$F$9+Positions!$E$6*Positions!$R$6*Stress!$G$9),(Positions!$E$6*Positions!$N$6*Stress!$C$10+Positions!$E$6*Positions!$O$6*Stress!$D$10+Positions!$E$6*Positions!$P$6*Stress!$E$10+Positions!$E$6*Positions!$Q$6*Stress!$F$10+Positions!$E$6*Positions!$R$6*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="16">
         <f>Liquidity!G6</f>
         <v/>
       </c>
-      <c r="I6" s="50">
+      <c r="I6" s="16">
         <f>ABS(E6)+G6+H6</f>
         <v/>
       </c>
-      <c r="J6" s="48">
+      <c r="J6" s="14">
         <f>IFERROR(I6/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="29">
-      <c r="B7" s="28">
+    <row r="7">
+      <c r="B7">
         <f>Positions!B7</f>
         <v/>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="16">
         <f>ABS(Positions!E7)</f>
         <v/>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$7*Positions!$N$7)*(Positions!$E$7*Positions!$N$7)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$7*Positions!$N$7)*(Positions!$E$7*Positions!$O$7)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$7*Positions!$N$7)*(Positions!$E$7*Positions!$P$7)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$7*Positions!$N$7)*(Positions!$E$7*Positions!$Q$7)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$7*Positions!$N$7)*(Positions!$E$7*Positions!$R$7)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$7*Positions!$O$7)*(Positions!$E$7*Positions!$N$7)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$7*Positions!$O$7)*(Positions!$E$7*Positions!$O$7)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$7*Positions!$O$7)*(Positions!$E$7*Positions!$P$7)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$7*Positions!$O$7)*(Positions!$E$7*Positions!$Q$7)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$7*Positions!$O$7)*(Positions!$E$7*Positions!$R$7)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$7*Positions!$P$7)*(Positions!$E$7*Positions!$N$7)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$7*Positions!$P$7)*(Positions!$E$7*Positions!$O$7)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$7*Positions!$P$7)*(Positions!$E$7*Positions!$P$7)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$7*Positions!$P$7)*(Positions!$E$7*Positions!$Q$7)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$7*Positions!$P$7)*(Positions!$E$7*Positions!$R$7)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$7*Positions!$Q$7)*(Positions!$E$7*Positions!$N$7)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$7*Positions!$Q$7)*(Positions!$E$7*Positions!$O$7)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$7*Positions!$Q$7)*(Positions!$E$7*Positions!$P$7)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$7*Positions!$Q$7)*(Positions!$E$7*Positions!$Q$7)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$7*Positions!$Q$7)*(Positions!$E$7*Positions!$R$7)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$7*Positions!$R$7)*(Positions!$E$7*Positions!$N$7)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$7*Positions!$R$7)*(Positions!$E$7*Positions!$O$7)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$7*Positions!$R$7)*(Positions!$E$7*Positions!$P$7)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$7*Positions!$R$7)*(Positions!$E$7*Positions!$Q$7)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$7*Positions!$R$7)*(Positions!$E$7*Positions!$R$7)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$7*Positions!$N$7)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$7*Positions!$N$7)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$7*Positions!$N$7)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$7*Positions!$N$7)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$7*Positions!$N$7)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$7*Positions!$O$7)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$7*Positions!$O$7)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$7*Positions!$O$7)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$7*Positions!$O$7)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$7*Positions!$O$7)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$7*Positions!$P$7)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$7*Positions!$P$7)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$7*Positions!$P$7)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$7*Positions!$P$7)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$7*Positions!$P$7)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$7*Positions!$Q$7)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$7*Positions!$Q$7)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$7*Positions!$Q$7)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$7*Positions!$Q$7)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$7*Positions!$Q$7)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$7*Positions!$R$7)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$7*Positions!$R$7)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$7*Positions!$R$7)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$7*Positions!$R$7)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$7*Positions!$R$7)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="14">
         <f>IFERROR(E7/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="16">
         <f>-MIN((Positions!$E$7*Positions!$N$7*Stress!$C$5+Positions!$E$7*Positions!$O$7*Stress!$D$5+Positions!$E$7*Positions!$P$7*Stress!$E$5+Positions!$E$7*Positions!$Q$7*Stress!$F$5+Positions!$E$7*Positions!$R$7*Stress!$G$5),(Positions!$E$7*Positions!$N$7*Stress!$C$6+Positions!$E$7*Positions!$O$7*Stress!$D$6+Positions!$E$7*Positions!$P$7*Stress!$E$6+Positions!$E$7*Positions!$Q$7*Stress!$F$6+Positions!$E$7*Positions!$R$7*Stress!$G$6),(Positions!$E$7*Positions!$N$7*Stress!$C$7+Positions!$E$7*Positions!$O$7*Stress!$D$7+Positions!$E$7*Positions!$P$7*Stress!$E$7+Positions!$E$7*Positions!$Q$7*Stress!$F$7+Positions!$E$7*Positions!$R$7*Stress!$G$7),(Positions!$E$7*Positions!$N$7*Stress!$C$8+Positions!$E$7*Positions!$O$7*Stress!$D$8+Positions!$E$7*Positions!$P$7*Stress!$E$8+Positions!$E$7*Positions!$Q$7*Stress!$F$8+Positions!$E$7*Positions!$R$7*Stress!$G$8),(Positions!$E$7*Positions!$N$7*Stress!$C$9+Positions!$E$7*Positions!$O$7*Stress!$D$9+Positions!$E$7*Positions!$P$7*Stress!$E$9+Positions!$E$7*Positions!$Q$7*Stress!$F$9+Positions!$E$7*Positions!$R$7*Stress!$G$9),(Positions!$E$7*Positions!$N$7*Stress!$C$10+Positions!$E$7*Positions!$O$7*Stress!$D$10+Positions!$E$7*Positions!$P$7*Stress!$E$10+Positions!$E$7*Positions!$Q$7*Stress!$F$10+Positions!$E$7*Positions!$R$7*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="16">
         <f>Liquidity!G7</f>
         <v/>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="16">
         <f>ABS(E7)+G7+H7</f>
         <v/>
       </c>
-      <c r="J7" s="48">
+      <c r="J7" s="14">
         <f>IFERROR(I7/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="29">
-      <c r="B8" s="28">
+    <row r="8">
+      <c r="B8">
         <f>Positions!B8</f>
         <v/>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="16">
         <f>ABS(Positions!E8)</f>
         <v/>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$8*Positions!$N$8)*(Positions!$E$8*Positions!$N$8)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$8*Positions!$N$8)*(Positions!$E$8*Positions!$O$8)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$8*Positions!$N$8)*(Positions!$E$8*Positions!$P$8)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$8*Positions!$N$8)*(Positions!$E$8*Positions!$Q$8)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$8*Positions!$N$8)*(Positions!$E$8*Positions!$R$8)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$8*Positions!$O$8)*(Positions!$E$8*Positions!$N$8)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$8*Positions!$O$8)*(Positions!$E$8*Positions!$O$8)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$8*Positions!$O$8)*(Positions!$E$8*Positions!$P$8)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$8*Positions!$O$8)*(Positions!$E$8*Positions!$Q$8)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$8*Positions!$O$8)*(Positions!$E$8*Positions!$R$8)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$8*Positions!$P$8)*(Positions!$E$8*Positions!$N$8)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$8*Positions!$P$8)*(Positions!$E$8*Positions!$O$8)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$8*Positions!$P$8)*(Positions!$E$8*Positions!$P$8)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$8*Positions!$P$8)*(Positions!$E$8*Positions!$Q$8)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$8*Positions!$P$8)*(Positions!$E$8*Positions!$R$8)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$8*Positions!$Q$8)*(Positions!$E$8*Positions!$N$8)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$8*Positions!$Q$8)*(Positions!$E$8*Positions!$O$8)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$8*Positions!$Q$8)*(Positions!$E$8*Positions!$P$8)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$8*Positions!$Q$8)*(Positions!$E$8*Positions!$Q$8)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$8*Positions!$Q$8)*(Positions!$E$8*Positions!$R$8)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$8*Positions!$R$8)*(Positions!$E$8*Positions!$N$8)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$8*Positions!$R$8)*(Positions!$E$8*Positions!$O$8)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$8*Positions!$R$8)*(Positions!$E$8*Positions!$P$8)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$8*Positions!$R$8)*(Positions!$E$8*Positions!$Q$8)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$8*Positions!$R$8)*(Positions!$E$8*Positions!$R$8)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$8*Positions!$N$8)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$8*Positions!$N$8)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$8*Positions!$N$8)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$8*Positions!$N$8)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$8*Positions!$N$8)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$8*Positions!$O$8)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$8*Positions!$O$8)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$8*Positions!$O$8)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$8*Positions!$O$8)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$8*Positions!$O$8)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$8*Positions!$P$8)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$8*Positions!$P$8)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$8*Positions!$P$8)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$8*Positions!$P$8)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$8*Positions!$P$8)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$8*Positions!$Q$8)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$8*Positions!$Q$8)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$8*Positions!$Q$8)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$8*Positions!$Q$8)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$8*Positions!$Q$8)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$8*Positions!$R$8)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$8*Positions!$R$8)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$8*Positions!$R$8)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$8*Positions!$R$8)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$8*Positions!$R$8)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="14">
         <f>IFERROR(E8/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="16">
         <f>-MIN((Positions!$E$8*Positions!$N$8*Stress!$C$5+Positions!$E$8*Positions!$O$8*Stress!$D$5+Positions!$E$8*Positions!$P$8*Stress!$E$5+Positions!$E$8*Positions!$Q$8*Stress!$F$5+Positions!$E$8*Positions!$R$8*Stress!$G$5),(Positions!$E$8*Positions!$N$8*Stress!$C$6+Positions!$E$8*Positions!$O$8*Stress!$D$6+Positions!$E$8*Positions!$P$8*Stress!$E$6+Positions!$E$8*Positions!$Q$8*Stress!$F$6+Positions!$E$8*Positions!$R$8*Stress!$G$6),(Positions!$E$8*Positions!$N$8*Stress!$C$7+Positions!$E$8*Positions!$O$8*Stress!$D$7+Positions!$E$8*Positions!$P$8*Stress!$E$7+Positions!$E$8*Positions!$Q$8*Stress!$F$7+Positions!$E$8*Positions!$R$8*Stress!$G$7),(Positions!$E$8*Positions!$N$8*Stress!$C$8+Positions!$E$8*Positions!$O$8*Stress!$D$8+Positions!$E$8*Positions!$P$8*Stress!$E$8+Positions!$E$8*Positions!$Q$8*Stress!$F$8+Positions!$E$8*Positions!$R$8*Stress!$G$8),(Positions!$E$8*Positions!$N$8*Stress!$C$9+Positions!$E$8*Positions!$O$8*Stress!$D$9+Positions!$E$8*Positions!$P$8*Stress!$E$9+Positions!$E$8*Positions!$Q$8*Stress!$F$9+Positions!$E$8*Positions!$R$8*Stress!$G$9),(Positions!$E$8*Positions!$N$8*Stress!$C$10+Positions!$E$8*Positions!$O$8*Stress!$D$10+Positions!$E$8*Positions!$P$8*Stress!$E$10+Positions!$E$8*Positions!$Q$8*Stress!$F$10+Positions!$E$8*Positions!$R$8*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="16">
         <f>Liquidity!G8</f>
         <v/>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="16">
         <f>ABS(E8)+G8+H8</f>
         <v/>
       </c>
-      <c r="J8" s="48">
+      <c r="J8" s="14">
         <f>IFERROR(I8/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="29">
-      <c r="B9" s="28">
+    <row r="9">
+      <c r="B9">
         <f>Positions!B9</f>
         <v/>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="16">
         <f>ABS(Positions!E9)</f>
         <v/>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$9*Positions!$N$9)*(Positions!$E$9*Positions!$N$9)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$9*Positions!$N$9)*(Positions!$E$9*Positions!$O$9)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$9*Positions!$N$9)*(Positions!$E$9*Positions!$P$9)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$9*Positions!$N$9)*(Positions!$E$9*Positions!$Q$9)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$9*Positions!$N$9)*(Positions!$E$9*Positions!$R$9)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$9*Positions!$O$9)*(Positions!$E$9*Positions!$N$9)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$9*Positions!$O$9)*(Positions!$E$9*Positions!$O$9)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$9*Positions!$O$9)*(Positions!$E$9*Positions!$P$9)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$9*Positions!$O$9)*(Positions!$E$9*Positions!$Q$9)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$9*Positions!$O$9)*(Positions!$E$9*Positions!$R$9)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$9*Positions!$P$9)*(Positions!$E$9*Positions!$N$9)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$9*Positions!$P$9)*(Positions!$E$9*Positions!$O$9)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$9*Positions!$P$9)*(Positions!$E$9*Positions!$P$9)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$9*Positions!$P$9)*(Positions!$E$9*Positions!$Q$9)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$9*Positions!$P$9)*(Positions!$E$9*Positions!$R$9)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$9*Positions!$Q$9)*(Positions!$E$9*Positions!$N$9)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$9*Positions!$Q$9)*(Positions!$E$9*Positions!$O$9)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$9*Positions!$Q$9)*(Positions!$E$9*Positions!$P$9)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$9*Positions!$Q$9)*(Positions!$E$9*Positions!$Q$9)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$9*Positions!$Q$9)*(Positions!$E$9*Positions!$R$9)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$9*Positions!$R$9)*(Positions!$E$9*Positions!$N$9)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$9*Positions!$R$9)*(Positions!$E$9*Positions!$O$9)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$9*Positions!$R$9)*(Positions!$E$9*Positions!$P$9)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$9*Positions!$R$9)*(Positions!$E$9*Positions!$Q$9)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$9*Positions!$R$9)*(Positions!$E$9*Positions!$R$9)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$9*Positions!$N$9)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$9*Positions!$N$9)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$9*Positions!$N$9)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$9*Positions!$N$9)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$9*Positions!$N$9)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$9*Positions!$O$9)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$9*Positions!$O$9)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$9*Positions!$O$9)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$9*Positions!$O$9)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$9*Positions!$O$9)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$9*Positions!$P$9)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$9*Positions!$P$9)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$9*Positions!$P$9)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$9*Positions!$P$9)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$9*Positions!$P$9)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$9*Positions!$Q$9)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$9*Positions!$Q$9)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$9*Positions!$Q$9)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$9*Positions!$Q$9)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$9*Positions!$Q$9)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$9*Positions!$R$9)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$9*Positions!$R$9)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$9*Positions!$R$9)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$9*Positions!$R$9)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$9*Positions!$R$9)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="14">
         <f>IFERROR(E9/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="16">
         <f>-MIN((Positions!$E$9*Positions!$N$9*Stress!$C$5+Positions!$E$9*Positions!$O$9*Stress!$D$5+Positions!$E$9*Positions!$P$9*Stress!$E$5+Positions!$E$9*Positions!$Q$9*Stress!$F$5+Positions!$E$9*Positions!$R$9*Stress!$G$5),(Positions!$E$9*Positions!$N$9*Stress!$C$6+Positions!$E$9*Positions!$O$9*Stress!$D$6+Positions!$E$9*Positions!$P$9*Stress!$E$6+Positions!$E$9*Positions!$Q$9*Stress!$F$6+Positions!$E$9*Positions!$R$9*Stress!$G$6),(Positions!$E$9*Positions!$N$9*Stress!$C$7+Positions!$E$9*Positions!$O$9*Stress!$D$7+Positions!$E$9*Positions!$P$9*Stress!$E$7+Positions!$E$9*Positions!$Q$9*Stress!$F$7+Positions!$E$9*Positions!$R$9*Stress!$G$7),(Positions!$E$9*Positions!$N$9*Stress!$C$8+Positions!$E$9*Positions!$O$9*Stress!$D$8+Positions!$E$9*Positions!$P$9*Stress!$E$8+Positions!$E$9*Positions!$Q$9*Stress!$F$8+Positions!$E$9*Positions!$R$9*Stress!$G$8),(Positions!$E$9*Positions!$N$9*Stress!$C$9+Positions!$E$9*Positions!$O$9*Stress!$D$9+Positions!$E$9*Positions!$P$9*Stress!$E$9+Positions!$E$9*Positions!$Q$9*Stress!$F$9+Positions!$E$9*Positions!$R$9*Stress!$G$9),(Positions!$E$9*Positions!$N$9*Stress!$C$10+Positions!$E$9*Positions!$O$9*Stress!$D$10+Positions!$E$9*Positions!$P$9*Stress!$E$10+Positions!$E$9*Positions!$Q$9*Stress!$F$10+Positions!$E$9*Positions!$R$9*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="16">
         <f>Liquidity!G9</f>
         <v/>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="16">
         <f>ABS(E9)+G9+H9</f>
         <v/>
       </c>
-      <c r="J9" s="48">
+      <c r="J9" s="14">
         <f>IFERROR(I9/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="29">
-      <c r="B10" s="28">
+    <row r="10">
+      <c r="B10">
         <f>Positions!B10</f>
         <v/>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="16">
         <f>ABS(Positions!E10)</f>
         <v/>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$10*Positions!$N$10)*(Positions!$E$10*Positions!$N$10)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$10*Positions!$N$10)*(Positions!$E$10*Positions!$O$10)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$10*Positions!$N$10)*(Positions!$E$10*Positions!$P$10)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$10*Positions!$N$10)*(Positions!$E$10*Positions!$Q$10)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$10*Positions!$N$10)*(Positions!$E$10*Positions!$R$10)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$10*Positions!$O$10)*(Positions!$E$10*Positions!$N$10)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$10*Positions!$O$10)*(Positions!$E$10*Positions!$O$10)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$10*Positions!$O$10)*(Positions!$E$10*Positions!$P$10)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$10*Positions!$O$10)*(Positions!$E$10*Positions!$Q$10)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$10*Positions!$O$10)*(Positions!$E$10*Positions!$R$10)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$10*Positions!$P$10)*(Positions!$E$10*Positions!$N$10)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$10*Positions!$P$10)*(Positions!$E$10*Positions!$O$10)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$10*Positions!$P$10)*(Positions!$E$10*Positions!$P$10)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$10*Positions!$P$10)*(Positions!$E$10*Positions!$Q$10)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$10*Positions!$P$10)*(Positions!$E$10*Positions!$R$10)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$10*Positions!$Q$10)*(Positions!$E$10*Positions!$N$10)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$10*Positions!$Q$10)*(Positions!$E$10*Positions!$O$10)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$10*Positions!$Q$10)*(Positions!$E$10*Positions!$P$10)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$10*Positions!$Q$10)*(Positions!$E$10*Positions!$Q$10)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$10*Positions!$Q$10)*(Positions!$E$10*Positions!$R$10)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$10*Positions!$R$10)*(Positions!$E$10*Positions!$N$10)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$10*Positions!$R$10)*(Positions!$E$10*Positions!$O$10)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$10*Positions!$R$10)*(Positions!$E$10*Positions!$P$10)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$10*Positions!$R$10)*(Positions!$E$10*Positions!$Q$10)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$10*Positions!$R$10)*(Positions!$E$10*Positions!$R$10)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$10*Positions!$N$10)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$10*Positions!$N$10)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$10*Positions!$N$10)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$10*Positions!$N$10)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$10*Positions!$N$10)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$10*Positions!$O$10)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$10*Positions!$O$10)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$10*Positions!$O$10)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$10*Positions!$O$10)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$10*Positions!$O$10)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$10*Positions!$P$10)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$10*Positions!$P$10)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$10*Positions!$P$10)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$10*Positions!$P$10)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$10*Positions!$P$10)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$10*Positions!$Q$10)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$10*Positions!$Q$10)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$10*Positions!$Q$10)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$10*Positions!$Q$10)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$10*Positions!$Q$10)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$10*Positions!$R$10)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$10*Positions!$R$10)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$10*Positions!$R$10)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$10*Positions!$R$10)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$10*Positions!$R$10)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="14">
         <f>IFERROR(E10/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="16">
         <f>-MIN((Positions!$E$10*Positions!$N$10*Stress!$C$5+Positions!$E$10*Positions!$O$10*Stress!$D$5+Positions!$E$10*Positions!$P$10*Stress!$E$5+Positions!$E$10*Positions!$Q$10*Stress!$F$5+Positions!$E$10*Positions!$R$10*Stress!$G$5),(Positions!$E$10*Positions!$N$10*Stress!$C$6+Positions!$E$10*Positions!$O$10*Stress!$D$6+Positions!$E$10*Positions!$P$10*Stress!$E$6+Positions!$E$10*Positions!$Q$10*Stress!$F$6+Positions!$E$10*Positions!$R$10*Stress!$G$6),(Positions!$E$10*Positions!$N$10*Stress!$C$7+Positions!$E$10*Positions!$O$10*Stress!$D$7+Positions!$E$10*Positions!$P$10*Stress!$E$7+Positions!$E$10*Positions!$Q$10*Stress!$F$7+Positions!$E$10*Positions!$R$10*Stress!$G$7),(Positions!$E$10*Positions!$N$10*Stress!$C$8+Positions!$E$10*Positions!$O$10*Stress!$D$8+Positions!$E$10*Positions!$P$10*Stress!$E$8+Positions!$E$10*Positions!$Q$10*Stress!$F$8+Positions!$E$10*Positions!$R$10*Stress!$G$8),(Positions!$E$10*Positions!$N$10*Stress!$C$9+Positions!$E$10*Positions!$O$10*Stress!$D$9+Positions!$E$10*Positions!$P$10*Stress!$E$9+Positions!$E$10*Positions!$Q$10*Stress!$F$9+Positions!$E$10*Positions!$R$10*Stress!$G$9),(Positions!$E$10*Positions!$N$10*Stress!$C$10+Positions!$E$10*Positions!$O$10*Stress!$D$10+Positions!$E$10*Positions!$P$10*Stress!$E$10+Positions!$E$10*Positions!$Q$10*Stress!$F$10+Positions!$E$10*Positions!$R$10*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="16">
         <f>Liquidity!G10</f>
         <v/>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="16">
         <f>ABS(E10)+G10+H10</f>
         <v/>
       </c>
-      <c r="J10" s="48">
+      <c r="J10" s="14">
         <f>IFERROR(I10/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="29">
-      <c r="B11" s="28">
+    <row r="11">
+      <c r="B11">
         <f>Positions!B11</f>
         <v/>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="16">
         <f>ABS(Positions!E11)</f>
         <v/>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$11*Positions!$N$11)*(Positions!$E$11*Positions!$N$11)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$11*Positions!$N$11)*(Positions!$E$11*Positions!$O$11)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$11*Positions!$N$11)*(Positions!$E$11*Positions!$P$11)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$11*Positions!$N$11)*(Positions!$E$11*Positions!$Q$11)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$11*Positions!$N$11)*(Positions!$E$11*Positions!$R$11)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$11*Positions!$O$11)*(Positions!$E$11*Positions!$N$11)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$11*Positions!$O$11)*(Positions!$E$11*Positions!$O$11)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$11*Positions!$O$11)*(Positions!$E$11*Positions!$P$11)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$11*Positions!$O$11)*(Positions!$E$11*Positions!$Q$11)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$11*Positions!$O$11)*(Positions!$E$11*Positions!$R$11)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$11*Positions!$P$11)*(Positions!$E$11*Positions!$N$11)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$11*Positions!$P$11)*(Positions!$E$11*Positions!$O$11)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$11*Positions!$P$11)*(Positions!$E$11*Positions!$P$11)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$11*Positions!$P$11)*(Positions!$E$11*Positions!$Q$11)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$11*Positions!$P$11)*(Positions!$E$11*Positions!$R$11)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$11*Positions!$Q$11)*(Positions!$E$11*Positions!$N$11)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$11*Positions!$Q$11)*(Positions!$E$11*Positions!$O$11)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$11*Positions!$Q$11)*(Positions!$E$11*Positions!$P$11)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$11*Positions!$Q$11)*(Positions!$E$11*Positions!$Q$11)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$11*Positions!$Q$11)*(Positions!$E$11*Positions!$R$11)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$11*Positions!$R$11)*(Positions!$E$11*Positions!$N$11)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$11*Positions!$R$11)*(Positions!$E$11*Positions!$O$11)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$11*Positions!$R$11)*(Positions!$E$11*Positions!$P$11)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$11*Positions!$R$11)*(Positions!$E$11*Positions!$Q$11)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$11*Positions!$R$11)*(Positions!$E$11*Positions!$R$11)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$11*Positions!$N$11)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$11*Positions!$N$11)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$11*Positions!$N$11)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$11*Positions!$N$11)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$11*Positions!$N$11)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$11*Positions!$O$11)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$11*Positions!$O$11)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$11*Positions!$O$11)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$11*Positions!$O$11)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$11*Positions!$O$11)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$11*Positions!$P$11)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$11*Positions!$P$11)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$11*Positions!$P$11)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$11*Positions!$P$11)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$11*Positions!$P$11)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$11*Positions!$Q$11)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$11*Positions!$Q$11)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$11*Positions!$Q$11)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$11*Positions!$Q$11)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$11*Positions!$Q$11)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$11*Positions!$R$11)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$11*Positions!$R$11)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$11*Positions!$R$11)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$11*Positions!$R$11)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$11*Positions!$R$11)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="14">
         <f>IFERROR(E11/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="16">
         <f>-MIN((Positions!$E$11*Positions!$N$11*Stress!$C$5+Positions!$E$11*Positions!$O$11*Stress!$D$5+Positions!$E$11*Positions!$P$11*Stress!$E$5+Positions!$E$11*Positions!$Q$11*Stress!$F$5+Positions!$E$11*Positions!$R$11*Stress!$G$5),(Positions!$E$11*Positions!$N$11*Stress!$C$6+Positions!$E$11*Positions!$O$11*Stress!$D$6+Positions!$E$11*Positions!$P$11*Stress!$E$6+Positions!$E$11*Positions!$Q$11*Stress!$F$6+Positions!$E$11*Positions!$R$11*Stress!$G$6),(Positions!$E$11*Positions!$N$11*Stress!$C$7+Positions!$E$11*Positions!$O$11*Stress!$D$7+Positions!$E$11*Positions!$P$11*Stress!$E$7+Positions!$E$11*Positions!$Q$11*Stress!$F$7+Positions!$E$11*Positions!$R$11*Stress!$G$7),(Positions!$E$11*Positions!$N$11*Stress!$C$8+Positions!$E$11*Positions!$O$11*Stress!$D$8+Positions!$E$11*Positions!$P$11*Stress!$E$8+Positions!$E$11*Positions!$Q$11*Stress!$F$8+Positions!$E$11*Positions!$R$11*Stress!$G$8),(Positions!$E$11*Positions!$N$11*Stress!$C$9+Positions!$E$11*Positions!$O$11*Stress!$D$9+Positions!$E$11*Positions!$P$11*Stress!$E$9+Positions!$E$11*Positions!$Q$11*Stress!$F$9+Positions!$E$11*Positions!$R$11*Stress!$G$9),(Positions!$E$11*Positions!$N$11*Stress!$C$10+Positions!$E$11*Positions!$O$11*Stress!$D$10+Positions!$E$11*Positions!$P$11*Stress!$E$10+Positions!$E$11*Positions!$Q$11*Stress!$F$10+Positions!$E$11*Positions!$R$11*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="16">
         <f>Liquidity!G11</f>
         <v/>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="16">
         <f>ABS(E11)+G11+H11</f>
         <v/>
       </c>
-      <c r="J11" s="48">
+      <c r="J11" s="14">
         <f>IFERROR(I11/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="29">
-      <c r="B12" s="28">
+    <row r="12">
+      <c r="B12">
         <f>Positions!B12</f>
         <v/>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="16">
         <f>ABS(Positions!E12)</f>
         <v/>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$12*Positions!$N$12)*(Positions!$E$12*Positions!$N$12)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$12*Positions!$N$12)*(Positions!$E$12*Positions!$O$12)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$12*Positions!$N$12)*(Positions!$E$12*Positions!$P$12)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$12*Positions!$N$12)*(Positions!$E$12*Positions!$Q$12)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$12*Positions!$N$12)*(Positions!$E$12*Positions!$R$12)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$12*Positions!$O$12)*(Positions!$E$12*Positions!$N$12)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$12*Positions!$O$12)*(Positions!$E$12*Positions!$O$12)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$12*Positions!$O$12)*(Positions!$E$12*Positions!$P$12)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$12*Positions!$O$12)*(Positions!$E$12*Positions!$Q$12)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$12*Positions!$O$12)*(Positions!$E$12*Positions!$R$12)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$12*Positions!$P$12)*(Positions!$E$12*Positions!$N$12)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$12*Positions!$P$12)*(Positions!$E$12*Positions!$O$12)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$12*Positions!$P$12)*(Positions!$E$12*Positions!$P$12)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$12*Positions!$P$12)*(Positions!$E$12*Positions!$Q$12)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$12*Positions!$P$12)*(Positions!$E$12*Positions!$R$12)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$12*Positions!$Q$12)*(Positions!$E$12*Positions!$N$12)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$12*Positions!$Q$12)*(Positions!$E$12*Positions!$O$12)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$12*Positions!$Q$12)*(Positions!$E$12*Positions!$P$12)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$12*Positions!$Q$12)*(Positions!$E$12*Positions!$Q$12)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$12*Positions!$Q$12)*(Positions!$E$12*Positions!$R$12)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$12*Positions!$R$12)*(Positions!$E$12*Positions!$N$12)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$12*Positions!$R$12)*(Positions!$E$12*Positions!$O$12)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$12*Positions!$R$12)*(Positions!$E$12*Positions!$P$12)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$12*Positions!$R$12)*(Positions!$E$12*Positions!$Q$12)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$12*Positions!$R$12)*(Positions!$E$12*Positions!$R$12)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$12*Positions!$N$12)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$12*Positions!$N$12)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$12*Positions!$N$12)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$12*Positions!$N$12)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$12*Positions!$N$12)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$12*Positions!$O$12)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$12*Positions!$O$12)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$12*Positions!$O$12)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$12*Positions!$O$12)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$12*Positions!$O$12)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$12*Positions!$P$12)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$12*Positions!$P$12)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$12*Positions!$P$12)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$12*Positions!$P$12)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$12*Positions!$P$12)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$12*Positions!$Q$12)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$12*Positions!$Q$12)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$12*Positions!$Q$12)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$12*Positions!$Q$12)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$12*Positions!$Q$12)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$12*Positions!$R$12)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$12*Positions!$R$12)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$12*Positions!$R$12)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$12*Positions!$R$12)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$12*Positions!$R$12)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="14">
         <f>IFERROR(E12/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="16">
         <f>-MIN((Positions!$E$12*Positions!$N$12*Stress!$C$5+Positions!$E$12*Positions!$O$12*Stress!$D$5+Positions!$E$12*Positions!$P$12*Stress!$E$5+Positions!$E$12*Positions!$Q$12*Stress!$F$5+Positions!$E$12*Positions!$R$12*Stress!$G$5),(Positions!$E$12*Positions!$N$12*Stress!$C$6+Positions!$E$12*Positions!$O$12*Stress!$D$6+Positions!$E$12*Positions!$P$12*Stress!$E$6+Positions!$E$12*Positions!$Q$12*Stress!$F$6+Positions!$E$12*Positions!$R$12*Stress!$G$6),(Positions!$E$12*Positions!$N$12*Stress!$C$7+Positions!$E$12*Positions!$O$12*Stress!$D$7+Positions!$E$12*Positions!$P$12*Stress!$E$7+Positions!$E$12*Positions!$Q$12*Stress!$F$7+Positions!$E$12*Positions!$R$12*Stress!$G$7),(Positions!$E$12*Positions!$N$12*Stress!$C$8+Positions!$E$12*Positions!$O$12*Stress!$D$8+Positions!$E$12*Positions!$P$12*Stress!$E$8+Positions!$E$12*Positions!$Q$12*Stress!$F$8+Positions!$E$12*Positions!$R$12*Stress!$G$8),(Positions!$E$12*Positions!$N$12*Stress!$C$9+Positions!$E$12*Positions!$O$12*Stress!$D$9+Positions!$E$12*Positions!$P$12*Stress!$E$9+Positions!$E$12*Positions!$Q$12*Stress!$F$9+Positions!$E$12*Positions!$R$12*Stress!$G$9),(Positions!$E$12*Positions!$N$12*Stress!$C$10+Positions!$E$12*Positions!$O$12*Stress!$D$10+Positions!$E$12*Positions!$P$12*Stress!$E$10+Positions!$E$12*Positions!$Q$12*Stress!$F$10+Positions!$E$12*Positions!$R$12*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="16">
         <f>Liquidity!G12</f>
         <v/>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="16">
         <f>ABS(E12)+G12+H12</f>
         <v/>
       </c>
-      <c r="J12" s="48">
+      <c r="J12" s="14">
         <f>IFERROR(I12/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="29">
-      <c r="B13" s="28">
+    <row r="13">
+      <c r="B13">
         <f>Positions!B13</f>
         <v/>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="16">
         <f>ABS(Positions!E13)</f>
         <v/>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$13*Positions!$N$13)*(Positions!$E$13*Positions!$N$13)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$13*Positions!$N$13)*(Positions!$E$13*Positions!$O$13)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$13*Positions!$N$13)*(Positions!$E$13*Positions!$P$13)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$13*Positions!$N$13)*(Positions!$E$13*Positions!$Q$13)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$13*Positions!$N$13)*(Positions!$E$13*Positions!$R$13)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$13*Positions!$O$13)*(Positions!$E$13*Positions!$N$13)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$13*Positions!$O$13)*(Positions!$E$13*Positions!$O$13)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$13*Positions!$O$13)*(Positions!$E$13*Positions!$P$13)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$13*Positions!$O$13)*(Positions!$E$13*Positions!$Q$13)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$13*Positions!$O$13)*(Positions!$E$13*Positions!$R$13)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$13*Positions!$P$13)*(Positions!$E$13*Positions!$N$13)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$13*Positions!$P$13)*(Positions!$E$13*Positions!$O$13)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$13*Positions!$P$13)*(Positions!$E$13*Positions!$P$13)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$13*Positions!$P$13)*(Positions!$E$13*Positions!$Q$13)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$13*Positions!$P$13)*(Positions!$E$13*Positions!$R$13)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$13*Positions!$Q$13)*(Positions!$E$13*Positions!$N$13)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$13*Positions!$Q$13)*(Positions!$E$13*Positions!$O$13)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$13*Positions!$Q$13)*(Positions!$E$13*Positions!$P$13)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$13*Positions!$Q$13)*(Positions!$E$13*Positions!$Q$13)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$13*Positions!$Q$13)*(Positions!$E$13*Positions!$R$13)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$13*Positions!$R$13)*(Positions!$E$13*Positions!$N$13)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$13*Positions!$R$13)*(Positions!$E$13*Positions!$O$13)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$13*Positions!$R$13)*(Positions!$E$13*Positions!$P$13)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$13*Positions!$R$13)*(Positions!$E$13*Positions!$Q$13)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$13*Positions!$R$13)*(Positions!$E$13*Positions!$R$13)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$13*Positions!$N$13)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$13*Positions!$N$13)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$13*Positions!$N$13)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$13*Positions!$N$13)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$13*Positions!$N$13)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$13*Positions!$O$13)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$13*Positions!$O$13)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$13*Positions!$O$13)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$13*Positions!$O$13)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$13*Positions!$O$13)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$13*Positions!$P$13)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$13*Positions!$P$13)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$13*Positions!$P$13)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$13*Positions!$P$13)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$13*Positions!$P$13)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$13*Positions!$Q$13)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$13*Positions!$Q$13)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$13*Positions!$Q$13)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$13*Positions!$Q$13)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$13*Positions!$Q$13)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$13*Positions!$R$13)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$13*Positions!$R$13)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$13*Positions!$R$13)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$13*Positions!$R$13)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$13*Positions!$R$13)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="14">
         <f>IFERROR(E13/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="16">
         <f>-MIN((Positions!$E$13*Positions!$N$13*Stress!$C$5+Positions!$E$13*Positions!$O$13*Stress!$D$5+Positions!$E$13*Positions!$P$13*Stress!$E$5+Positions!$E$13*Positions!$Q$13*Stress!$F$5+Positions!$E$13*Positions!$R$13*Stress!$G$5),(Positions!$E$13*Positions!$N$13*Stress!$C$6+Positions!$E$13*Positions!$O$13*Stress!$D$6+Positions!$E$13*Positions!$P$13*Stress!$E$6+Positions!$E$13*Positions!$Q$13*Stress!$F$6+Positions!$E$13*Positions!$R$13*Stress!$G$6),(Positions!$E$13*Positions!$N$13*Stress!$C$7+Positions!$E$13*Positions!$O$13*Stress!$D$7+Positions!$E$13*Positions!$P$13*Stress!$E$7+Positions!$E$13*Positions!$Q$13*Stress!$F$7+Positions!$E$13*Positions!$R$13*Stress!$G$7),(Positions!$E$13*Positions!$N$13*Stress!$C$8+Positions!$E$13*Positions!$O$13*Stress!$D$8+Positions!$E$13*Positions!$P$13*Stress!$E$8+Positions!$E$13*Positions!$Q$13*Stress!$F$8+Positions!$E$13*Positions!$R$13*Stress!$G$8),(Positions!$E$13*Positions!$N$13*Stress!$C$9+Positions!$E$13*Positions!$O$13*Stress!$D$9+Positions!$E$13*Positions!$P$13*Stress!$E$9+Positions!$E$13*Positions!$Q$13*Stress!$F$9+Positions!$E$13*Positions!$R$13*Stress!$G$9),(Positions!$E$13*Positions!$N$13*Stress!$C$10+Positions!$E$13*Positions!$O$13*Stress!$D$10+Positions!$E$13*Positions!$P$13*Stress!$E$10+Positions!$E$13*Positions!$Q$13*Stress!$F$10+Positions!$E$13*Positions!$R$13*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="16">
         <f>Liquidity!G13</f>
         <v/>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="16">
         <f>ABS(E13)+G13+H13</f>
         <v/>
       </c>
-      <c r="J13" s="48">
+      <c r="J13" s="14">
         <f>IFERROR(I13/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="29">
-      <c r="B14" s="28">
+    <row r="14">
+      <c r="B14">
         <f>Positions!B14</f>
         <v/>
       </c>
-      <c r="C14" s="50">
+      <c r="C14" s="16">
         <f>ABS(Positions!E14)</f>
         <v/>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$14*Positions!$N$14)*(Positions!$E$14*Positions!$N$14)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$14*Positions!$N$14)*(Positions!$E$14*Positions!$O$14)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$14*Positions!$N$14)*(Positions!$E$14*Positions!$P$14)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$14*Positions!$N$14)*(Positions!$E$14*Positions!$Q$14)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$14*Positions!$N$14)*(Positions!$E$14*Positions!$R$14)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$14*Positions!$O$14)*(Positions!$E$14*Positions!$N$14)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$14*Positions!$O$14)*(Positions!$E$14*Positions!$O$14)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$14*Positions!$O$14)*(Positions!$E$14*Positions!$P$14)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$14*Positions!$O$14)*(Positions!$E$14*Positions!$Q$14)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$14*Positions!$O$14)*(Positions!$E$14*Positions!$R$14)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$14*Positions!$P$14)*(Positions!$E$14*Positions!$N$14)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$14*Positions!$P$14)*(Positions!$E$14*Positions!$O$14)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$14*Positions!$P$14)*(Positions!$E$14*Positions!$P$14)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$14*Positions!$P$14)*(Positions!$E$14*Positions!$Q$14)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$14*Positions!$P$14)*(Positions!$E$14*Positions!$R$14)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$14*Positions!$Q$14)*(Positions!$E$14*Positions!$N$14)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$14*Positions!$Q$14)*(Positions!$E$14*Positions!$O$14)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$14*Positions!$Q$14)*(Positions!$E$14*Positions!$P$14)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$14*Positions!$Q$14)*(Positions!$E$14*Positions!$Q$14)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$14*Positions!$Q$14)*(Positions!$E$14*Positions!$R$14)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$14*Positions!$R$14)*(Positions!$E$14*Positions!$N$14)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$14*Positions!$R$14)*(Positions!$E$14*Positions!$O$14)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$14*Positions!$R$14)*(Positions!$E$14*Positions!$P$14)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$14*Positions!$R$14)*(Positions!$E$14*Positions!$Q$14)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$14*Positions!$R$14)*(Positions!$E$14*Positions!$R$14)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$14*Positions!$N$14)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$14*Positions!$N$14)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$14*Positions!$N$14)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$14*Positions!$N$14)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$14*Positions!$N$14)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$14*Positions!$O$14)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$14*Positions!$O$14)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$14*Positions!$O$14)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$14*Positions!$O$14)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$14*Positions!$O$14)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$14*Positions!$P$14)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$14*Positions!$P$14)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$14*Positions!$P$14)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$14*Positions!$P$14)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$14*Positions!$P$14)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$14*Positions!$Q$14)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$14*Positions!$Q$14)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$14*Positions!$Q$14)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$14*Positions!$Q$14)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$14*Positions!$Q$14)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$14*Positions!$R$14)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$14*Positions!$R$14)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$14*Positions!$R$14)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$14*Positions!$R$14)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$14*Positions!$R$14)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="14">
         <f>IFERROR(E14/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="16">
         <f>-MIN((Positions!$E$14*Positions!$N$14*Stress!$C$5+Positions!$E$14*Positions!$O$14*Stress!$D$5+Positions!$E$14*Positions!$P$14*Stress!$E$5+Positions!$E$14*Positions!$Q$14*Stress!$F$5+Positions!$E$14*Positions!$R$14*Stress!$G$5),(Positions!$E$14*Positions!$N$14*Stress!$C$6+Positions!$E$14*Positions!$O$14*Stress!$D$6+Positions!$E$14*Positions!$P$14*Stress!$E$6+Positions!$E$14*Positions!$Q$14*Stress!$F$6+Positions!$E$14*Positions!$R$14*Stress!$G$6),(Positions!$E$14*Positions!$N$14*Stress!$C$7+Positions!$E$14*Positions!$O$14*Stress!$D$7+Positions!$E$14*Positions!$P$14*Stress!$E$7+Positions!$E$14*Positions!$Q$14*Stress!$F$7+Positions!$E$14*Positions!$R$14*Stress!$G$7),(Positions!$E$14*Positions!$N$14*Stress!$C$8+Positions!$E$14*Positions!$O$14*Stress!$D$8+Positions!$E$14*Positions!$P$14*Stress!$E$8+Positions!$E$14*Positions!$Q$14*Stress!$F$8+Positions!$E$14*Positions!$R$14*Stress!$G$8),(Positions!$E$14*Positions!$N$14*Stress!$C$9+Positions!$E$14*Positions!$O$14*Stress!$D$9+Positions!$E$14*Positions!$P$14*Stress!$E$9+Positions!$E$14*Positions!$Q$14*Stress!$F$9+Positions!$E$14*Positions!$R$14*Stress!$G$9),(Positions!$E$14*Positions!$N$14*Stress!$C$10+Positions!$E$14*Positions!$O$14*Stress!$D$10+Positions!$E$14*Positions!$P$14*Stress!$E$10+Positions!$E$14*Positions!$Q$14*Stress!$F$10+Positions!$E$14*Positions!$R$14*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="16">
         <f>Liquidity!G14</f>
         <v/>
       </c>
-      <c r="I14" s="50">
+      <c r="I14" s="16">
         <f>ABS(E14)+G14+H14</f>
         <v/>
       </c>
-      <c r="J14" s="48">
+      <c r="J14" s="14">
         <f>IFERROR(I14/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="29">
-      <c r="B15" s="28">
+    <row r="15">
+      <c r="B15">
         <f>Positions!B15</f>
         <v/>
       </c>
-      <c r="C15" s="50">
+      <c r="C15" s="16">
         <f>ABS(Positions!E15)</f>
         <v/>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$15*Positions!$N$15)*(Positions!$E$15*Positions!$N$15)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$15*Positions!$N$15)*(Positions!$E$15*Positions!$O$15)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$15*Positions!$N$15)*(Positions!$E$15*Positions!$P$15)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$15*Positions!$N$15)*(Positions!$E$15*Positions!$Q$15)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$15*Positions!$N$15)*(Positions!$E$15*Positions!$R$15)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$15*Positions!$O$15)*(Positions!$E$15*Positions!$N$15)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$15*Positions!$O$15)*(Positions!$E$15*Positions!$O$15)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$15*Positions!$O$15)*(Positions!$E$15*Positions!$P$15)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$15*Positions!$O$15)*(Positions!$E$15*Positions!$Q$15)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$15*Positions!$O$15)*(Positions!$E$15*Positions!$R$15)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$15*Positions!$P$15)*(Positions!$E$15*Positions!$N$15)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$15*Positions!$P$15)*(Positions!$E$15*Positions!$O$15)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$15*Positions!$P$15)*(Positions!$E$15*Positions!$P$15)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$15*Positions!$P$15)*(Positions!$E$15*Positions!$Q$15)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$15*Positions!$P$15)*(Positions!$E$15*Positions!$R$15)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$15*Positions!$Q$15)*(Positions!$E$15*Positions!$N$15)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$15*Positions!$Q$15)*(Positions!$E$15*Positions!$O$15)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$15*Positions!$Q$15)*(Positions!$E$15*Positions!$P$15)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$15*Positions!$Q$15)*(Positions!$E$15*Positions!$Q$15)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$15*Positions!$Q$15)*(Positions!$E$15*Positions!$R$15)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$15*Positions!$R$15)*(Positions!$E$15*Positions!$N$15)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$15*Positions!$R$15)*(Positions!$E$15*Positions!$O$15)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$15*Positions!$R$15)*(Positions!$E$15*Positions!$P$15)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$15*Positions!$R$15)*(Positions!$E$15*Positions!$Q$15)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$15*Positions!$R$15)*(Positions!$E$15*Positions!$R$15)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$15*Positions!$N$15)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$15*Positions!$N$15)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$15*Positions!$N$15)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$15*Positions!$N$15)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$15*Positions!$N$15)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$15*Positions!$O$15)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$15*Positions!$O$15)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$15*Positions!$O$15)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$15*Positions!$O$15)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$15*Positions!$O$15)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$15*Positions!$P$15)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$15*Positions!$P$15)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$15*Positions!$P$15)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$15*Positions!$P$15)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$15*Positions!$P$15)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$15*Positions!$Q$15)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$15*Positions!$Q$15)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$15*Positions!$Q$15)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$15*Positions!$Q$15)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$15*Positions!$Q$15)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$15*Positions!$R$15)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$15*Positions!$R$15)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$15*Positions!$R$15)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$15*Positions!$R$15)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$15*Positions!$R$15)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="14">
         <f>IFERROR(E15/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="16">
         <f>-MIN((Positions!$E$15*Positions!$N$15*Stress!$C$5+Positions!$E$15*Positions!$O$15*Stress!$D$5+Positions!$E$15*Positions!$P$15*Stress!$E$5+Positions!$E$15*Positions!$Q$15*Stress!$F$5+Positions!$E$15*Positions!$R$15*Stress!$G$5),(Positions!$E$15*Positions!$N$15*Stress!$C$6+Positions!$E$15*Positions!$O$15*Stress!$D$6+Positions!$E$15*Positions!$P$15*Stress!$E$6+Positions!$E$15*Positions!$Q$15*Stress!$F$6+Positions!$E$15*Positions!$R$15*Stress!$G$6),(Positions!$E$15*Positions!$N$15*Stress!$C$7+Positions!$E$15*Positions!$O$15*Stress!$D$7+Positions!$E$15*Positions!$P$15*Stress!$E$7+Positions!$E$15*Positions!$Q$15*Stress!$F$7+Positions!$E$15*Positions!$R$15*Stress!$G$7),(Positions!$E$15*Positions!$N$15*Stress!$C$8+Positions!$E$15*Positions!$O$15*Stress!$D$8+Positions!$E$15*Positions!$P$15*Stress!$E$8+Positions!$E$15*Positions!$Q$15*Stress!$F$8+Positions!$E$15*Positions!$R$15*Stress!$G$8),(Positions!$E$15*Positions!$N$15*Stress!$C$9+Positions!$E$15*Positions!$O$15*Stress!$D$9+Positions!$E$15*Positions!$P$15*Stress!$E$9+Positions!$E$15*Positions!$Q$15*Stress!$F$9+Positions!$E$15*Positions!$R$15*Stress!$G$9),(Positions!$E$15*Positions!$N$15*Stress!$C$10+Positions!$E$15*Positions!$O$15*Stress!$D$10+Positions!$E$15*Positions!$P$15*Stress!$E$10+Positions!$E$15*Positions!$Q$15*Stress!$F$10+Positions!$E$15*Positions!$R$15*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H15" s="50">
+      <c r="H15" s="16">
         <f>Liquidity!G15</f>
         <v/>
       </c>
-      <c r="I15" s="50">
+      <c r="I15" s="16">
         <f>ABS(E15)+G15+H15</f>
         <v/>
       </c>
-      <c r="J15" s="48">
+      <c r="J15" s="14">
         <f>IFERROR(I15/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="29">
-      <c r="B16" s="28">
+    <row r="16">
+      <c r="B16">
         <f>Positions!B16</f>
         <v/>
       </c>
-      <c r="C16" s="50">
+      <c r="C16" s="16">
         <f>ABS(Positions!E16)</f>
         <v/>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="16">
         <f>'VaR &amp; ES'!$C$7*SQRT(MAX(0,((Positions!$E$16*Positions!$N$16)*(Positions!$E$16*Positions!$N$16)*Factors!$D$5*Factors!$D$5*Factors!$E$5+(Positions!$E$16*Positions!$N$16)*(Positions!$E$16*Positions!$O$16)*Factors!$D$5*Factors!$D$6*Factors!$F$5+(Positions!$E$16*Positions!$N$16)*(Positions!$E$16*Positions!$P$16)*Factors!$D$5*Factors!$D$7*Factors!$G$5+(Positions!$E$16*Positions!$N$16)*(Positions!$E$16*Positions!$Q$16)*Factors!$D$5*Factors!$D$8*Factors!$H$5+(Positions!$E$16*Positions!$N$16)*(Positions!$E$16*Positions!$R$16)*Factors!$D$5*Factors!$D$9*Factors!$I$5+(Positions!$E$16*Positions!$O$16)*(Positions!$E$16*Positions!$N$16)*Factors!$D$6*Factors!$D$5*Factors!$E$6+(Positions!$E$16*Positions!$O$16)*(Positions!$E$16*Positions!$O$16)*Factors!$D$6*Factors!$D$6*Factors!$F$6+(Positions!$E$16*Positions!$O$16)*(Positions!$E$16*Positions!$P$16)*Factors!$D$6*Factors!$D$7*Factors!$G$6+(Positions!$E$16*Positions!$O$16)*(Positions!$E$16*Positions!$Q$16)*Factors!$D$6*Factors!$D$8*Factors!$H$6+(Positions!$E$16*Positions!$O$16)*(Positions!$E$16*Positions!$R$16)*Factors!$D$6*Factors!$D$9*Factors!$I$6+(Positions!$E$16*Positions!$P$16)*(Positions!$E$16*Positions!$N$16)*Factors!$D$7*Factors!$D$5*Factors!$E$7+(Positions!$E$16*Positions!$P$16)*(Positions!$E$16*Positions!$O$16)*Factors!$D$7*Factors!$D$6*Factors!$F$7+(Positions!$E$16*Positions!$P$16)*(Positions!$E$16*Positions!$P$16)*Factors!$D$7*Factors!$D$7*Factors!$G$7+(Positions!$E$16*Positions!$P$16)*(Positions!$E$16*Positions!$Q$16)*Factors!$D$7*Factors!$D$8*Factors!$H$7+(Positions!$E$16*Positions!$P$16)*(Positions!$E$16*Positions!$R$16)*Factors!$D$7*Factors!$D$9*Factors!$I$7+(Positions!$E$16*Positions!$Q$16)*(Positions!$E$16*Positions!$N$16)*Factors!$D$8*Factors!$D$5*Factors!$E$8+(Positions!$E$16*Positions!$Q$16)*(Positions!$E$16*Positions!$O$16)*Factors!$D$8*Factors!$D$6*Factors!$F$8+(Positions!$E$16*Positions!$Q$16)*(Positions!$E$16*Positions!$P$16)*Factors!$D$8*Factors!$D$7*Factors!$G$8+(Positions!$E$16*Positions!$Q$16)*(Positions!$E$16*Positions!$Q$16)*Factors!$D$8*Factors!$D$8*Factors!$H$8+(Positions!$E$16*Positions!$Q$16)*(Positions!$E$16*Positions!$R$16)*Factors!$D$8*Factors!$D$9*Factors!$I$8+(Positions!$E$16*Positions!$R$16)*(Positions!$E$16*Positions!$N$16)*Factors!$D$9*Factors!$D$5*Factors!$E$9+(Positions!$E$16*Positions!$R$16)*(Positions!$E$16*Positions!$O$16)*Factors!$D$9*Factors!$D$6*Factors!$F$9+(Positions!$E$16*Positions!$R$16)*(Positions!$E$16*Positions!$P$16)*Factors!$D$9*Factors!$D$7*Factors!$G$9+(Positions!$E$16*Positions!$R$16)*(Positions!$E$16*Positions!$Q$16)*Factors!$D$9*Factors!$D$8*Factors!$H$9+(Positions!$E$16*Positions!$R$16)*(Positions!$E$16*Positions!$R$16)*Factors!$D$9*Factors!$D$9*Factors!$I$9)/Assumptions!$E$6))</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="16">
         <f>IFERROR('VaR &amp; ES'!$C$7*((Positions!$E$16*Positions!$N$16)*Factors!$D$5*Factors!$C$5*Factors!$D$5*Factors!$E$5+(Positions!$E$16*Positions!$N$16)*Factors!$D$5*Factors!$C$6*Factors!$D$6*Factors!$F$5+(Positions!$E$16*Positions!$N$16)*Factors!$D$5*Factors!$C$7*Factors!$D$7*Factors!$G$5+(Positions!$E$16*Positions!$N$16)*Factors!$D$5*Factors!$C$8*Factors!$D$8*Factors!$H$5+(Positions!$E$16*Positions!$N$16)*Factors!$D$5*Factors!$C$9*Factors!$D$9*Factors!$I$5+(Positions!$E$16*Positions!$O$16)*Factors!$D$6*Factors!$C$5*Factors!$D$5*Factors!$E$6+(Positions!$E$16*Positions!$O$16)*Factors!$D$6*Factors!$C$6*Factors!$D$6*Factors!$F$6+(Positions!$E$16*Positions!$O$16)*Factors!$D$6*Factors!$C$7*Factors!$D$7*Factors!$G$6+(Positions!$E$16*Positions!$O$16)*Factors!$D$6*Factors!$C$8*Factors!$D$8*Factors!$H$6+(Positions!$E$16*Positions!$O$16)*Factors!$D$6*Factors!$C$9*Factors!$D$9*Factors!$I$6+(Positions!$E$16*Positions!$P$16)*Factors!$D$7*Factors!$C$5*Factors!$D$5*Factors!$E$7+(Positions!$E$16*Positions!$P$16)*Factors!$D$7*Factors!$C$6*Factors!$D$6*Factors!$F$7+(Positions!$E$16*Positions!$P$16)*Factors!$D$7*Factors!$C$7*Factors!$D$7*Factors!$G$7+(Positions!$E$16*Positions!$P$16)*Factors!$D$7*Factors!$C$8*Factors!$D$8*Factors!$H$7+(Positions!$E$16*Positions!$P$16)*Factors!$D$7*Factors!$C$9*Factors!$D$9*Factors!$I$7+(Positions!$E$16*Positions!$Q$16)*Factors!$D$8*Factors!$C$5*Factors!$D$5*Factors!$E$8+(Positions!$E$16*Positions!$Q$16)*Factors!$D$8*Factors!$C$6*Factors!$D$6*Factors!$F$8+(Positions!$E$16*Positions!$Q$16)*Factors!$D$8*Factors!$C$7*Factors!$D$7*Factors!$G$8+(Positions!$E$16*Positions!$Q$16)*Factors!$D$8*Factors!$C$8*Factors!$D$8*Factors!$H$8+(Positions!$E$16*Positions!$Q$16)*Factors!$D$8*Factors!$C$9*Factors!$D$9*Factors!$I$8+(Positions!$E$16*Positions!$R$16)*Factors!$D$9*Factors!$C$5*Factors!$D$5*Factors!$E$9+(Positions!$E$16*Positions!$R$16)*Factors!$D$9*Factors!$C$6*Factors!$D$6*Factors!$F$9+(Positions!$E$16*Positions!$R$16)*Factors!$D$9*Factors!$C$7*Factors!$D$7*Factors!$G$9+(Positions!$E$16*Positions!$R$16)*Factors!$D$9*Factors!$C$8*Factors!$D$8*Factors!$H$9+(Positions!$E$16*Positions!$R$16)*Factors!$D$9*Factors!$C$9*Factors!$D$9*Factors!$I$9)/(Factors!$C$13*SQRT(Assumptions!$E$6)),0)</f>
         <v/>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="14">
         <f>IFERROR(E16/'VaR &amp; ES'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="16">
         <f>-MIN((Positions!$E$16*Positions!$N$16*Stress!$C$5+Positions!$E$16*Positions!$O$16*Stress!$D$5+Positions!$E$16*Positions!$P$16*Stress!$E$5+Positions!$E$16*Positions!$Q$16*Stress!$F$5+Positions!$E$16*Positions!$R$16*Stress!$G$5),(Positions!$E$16*Positions!$N$16*Stress!$C$6+Positions!$E$16*Positions!$O$16*Stress!$D$6+Positions!$E$16*Positions!$P$16*Stress!$E$6+Positions!$E$16*Positions!$Q$16*Stress!$F$6+Positions!$E$16*Positions!$R$16*Stress!$G$6),(Positions!$E$16*Positions!$N$16*Stress!$C$7+Positions!$E$16*Positions!$O$16*Stress!$D$7+Positions!$E$16*Positions!$P$16*Stress!$E$7+Positions!$E$16*Positions!$Q$16*Stress!$F$7+Positions!$E$16*Positions!$R$16*Stress!$G$7),(Positions!$E$16*Positions!$N$16*Stress!$C$8+Positions!$E$16*Positions!$O$16*Stress!$D$8+Positions!$E$16*Positions!$P$16*Stress!$E$8+Positions!$E$16*Positions!$Q$16*Stress!$F$8+Positions!$E$16*Positions!$R$16*Stress!$G$8),(Positions!$E$16*Positions!$N$16*Stress!$C$9+Positions!$E$16*Positions!$O$16*Stress!$D$9+Positions!$E$16*Positions!$P$16*Stress!$E$9+Positions!$E$16*Positions!$Q$16*Stress!$F$9+Positions!$E$16*Positions!$R$16*Stress!$G$9),(Positions!$E$16*Positions!$N$16*Stress!$C$10+Positions!$E$16*Positions!$O$16*Stress!$D$10+Positions!$E$16*Positions!$P$16*Stress!$E$10+Positions!$E$16*Positions!$Q$16*Stress!$F$10+Positions!$E$16*Positions!$R$16*Stress!$G$10))</f>
         <v/>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="16">
         <f>Liquidity!G16</f>
         <v/>
       </c>
-      <c r="I16" s="50">
+      <c r="I16" s="16">
         <f>ABS(E16)+G16+H16</f>
         <v/>
       </c>
-      <c r="J16" s="48">
+      <c r="J16" s="14">
         <f>IFERROR(I16/SUM($I$5:$I$16),0)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="29">
-      <c r="B18" s="54" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Portfolio total</t>
         </is>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="21">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="21">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="21">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F18" s="57">
+      <c r="F18" s="25">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="21">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="21">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="I18" s="55">
+      <c r="I18" s="21">
         <f>SUM(I5:I16)</f>
         <v/>
       </c>
-      <c r="J18" s="57">
+      <c r="J18" s="25">
         <f>SUM(J5:J16)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="29">
-      <c r="B20" s="28" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Component VaR reconciliation</t>
         </is>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="16">
         <f>E18-'VaR &amp; ES'!C8</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20">
         <f>IF(ABS(C20)&lt;0.01,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="29">
-      <c r="B21" s="28" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Largest risk concentration</t>
         </is>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="14">
         <f>MAX(J5:J16)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="29">
-      <c r="B22" s="28" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Largest contributor</t>
         </is>
       </c>
-      <c r="C22" s="28">
+      <c r="C22">
         <f>INDEX(B5:B16,MATCH(MAX(J5:J16),J5:J16,0))</f>
         <v/>
       </c>
@@ -6251,21 +6191,19 @@
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="D20">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>D20="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>D20="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>D20="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>D20="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>